--- a/daily/2026-04-02.xlsx
+++ b/daily/2026-04-02.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X84"/>
+  <dimension ref="A1:X86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,7 +715,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -729,71 +729,75 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7</v>
+        <v>17.7</v>
       </c>
       <c r="F4" t="n">
-        <v>15.6</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>16.9</v>
+        <v>22.1</v>
       </c>
       <c r="H4" t="n">
-        <v>18.4</v>
+        <v>20.9</v>
       </c>
       <c r="I4" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>27.1</v>
+        <v>28.5</v>
       </c>
       <c r="K4" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="L4" t="n">
-        <v>39.9</v>
+        <v>43.4</v>
       </c>
       <c r="M4" t="n">
-        <v>38.8</v>
+        <v>40.1</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="P4" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>21</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>26.3 (3g)</t>
+        </is>
+      </c>
       <c r="X4" t="n">
-        <v>12.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,75 +811,75 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="E5" t="n">
-        <v>17.7</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>28.6</v>
       </c>
       <c r="G5" t="n">
-        <v>22.1</v>
+        <v>28.4</v>
       </c>
       <c r="H5" t="n">
-        <v>20.9</v>
+        <v>26.8</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>26.1</v>
       </c>
       <c r="J5" t="n">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
-        <v>28.1</v>
+        <v>32.4</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4</v>
+        <v>48.4</v>
       </c>
       <c r="M5" t="n">
-        <v>40.1</v>
+        <v>45</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>7.9</v>
       </c>
       <c r="O5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.4</v>
-      </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>26.3 (3g)</t>
+          <t>33.0 (3g)</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>-1.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -885,79 +889,75 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>4.7</v>
       </c>
       <c r="F6" t="n">
-        <v>20.2</v>
+        <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>20.6</v>
+        <v>6.9</v>
       </c>
       <c r="H6" t="n">
-        <v>19.9</v>
+        <v>6.7</v>
       </c>
       <c r="I6" t="n">
-        <v>17.1</v>
+        <v>6.7</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>17.6</v>
       </c>
       <c r="K6" t="n">
-        <v>25.3</v>
+        <v>18.3</v>
       </c>
       <c r="L6" t="n">
-        <v>43.6</v>
+        <v>83</v>
       </c>
       <c r="M6" t="n">
-        <v>38.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>-1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>4.8</v>
+        <v>12.9</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7</v>
+        <v>-0.6</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="V6" t="n">
-        <v>21</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>19.3 (3g)</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -967,79 +967,75 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>28.6</v>
+        <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>28.4</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>26.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7" t="n">
-        <v>26.1</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>33</v>
+        <v>27.4</v>
       </c>
       <c r="K7" t="n">
-        <v>32.4</v>
+        <v>27.9</v>
       </c>
       <c r="L7" t="n">
-        <v>48.4</v>
+        <v>60.5</v>
       </c>
       <c r="M7" t="n">
-        <v>45</v>
+        <v>61.9</v>
       </c>
       <c r="N7" t="n">
-        <v>7.9</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.6</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>-1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="U7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7" t="n">
-        <v>21</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>33.0 (3g)</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>6.5</v>
+        <v>-35.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1049,75 +1045,79 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7</v>
+        <v>14.3</v>
       </c>
       <c r="F8" t="n">
-        <v>4.8</v>
+        <v>17.4</v>
       </c>
       <c r="G8" t="n">
-        <v>6.9</v>
+        <v>17.7</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7</v>
+        <v>15.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.7</v>
+        <v>16.1</v>
       </c>
       <c r="J8" t="n">
-        <v>17.6</v>
+        <v>20.9</v>
       </c>
       <c r="K8" t="n">
-        <v>18.3</v>
+        <v>24.1</v>
       </c>
       <c r="L8" t="n">
-        <v>83</v>
+        <v>47.7</v>
       </c>
       <c r="M8" t="n">
-        <v>70.09999999999999</v>
+        <v>41.9</v>
       </c>
       <c r="N8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>70</v>
+      </c>
+      <c r="P8" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>60</v>
-      </c>
-      <c r="P8" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16</v>
       </c>
       <c r="V8" t="n">
         <v>22</v>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>17.0 (3g)</t>
+        </is>
+      </c>
       <c r="X8" t="n">
-        <v>-11</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1127,75 +1127,75 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="F9" t="n">
-        <v>8.6</v>
+        <v>14.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.1</v>
+        <v>16.4</v>
       </c>
       <c r="H9" t="n">
-        <v>7.5</v>
+        <v>18.7</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>18.7</v>
       </c>
       <c r="J9" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="K9" t="n">
-        <v>27.9</v>
+        <v>30.5</v>
       </c>
       <c r="L9" t="n">
-        <v>60.5</v>
+        <v>43.2</v>
       </c>
       <c r="M9" t="n">
-        <v>61.9</v>
+        <v>47.6</v>
       </c>
       <c r="N9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6</v>
+        <v>-4.3</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5</v>
+        <v>-4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
         <v>22</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
-        <v>-35.6</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1205,79 +1205,79 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="E10" t="n">
-        <v>14.3</v>
+        <v>22.3</v>
       </c>
       <c r="F10" t="n">
-        <v>17.4</v>
+        <v>20.2</v>
       </c>
       <c r="G10" t="n">
-        <v>17.7</v>
+        <v>19</v>
       </c>
       <c r="H10" t="n">
-        <v>15.8</v>
+        <v>20.1</v>
       </c>
       <c r="I10" t="n">
-        <v>16.1</v>
+        <v>20.8</v>
       </c>
       <c r="J10" t="n">
-        <v>20.9</v>
+        <v>30.5</v>
       </c>
       <c r="K10" t="n">
-        <v>24.1</v>
+        <v>30.2</v>
       </c>
       <c r="L10" t="n">
-        <v>47.7</v>
+        <v>45.6</v>
       </c>
       <c r="M10" t="n">
-        <v>41.9</v>
+        <v>46.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>-0.6</v>
       </c>
       <c r="S10" t="n">
-        <v>5.9</v>
+        <v>-0.7</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.2</v>
+        <v>0.3</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V10" t="n">
         <v>22</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>17.0 (3g)</t>
+          <t>14.3 (3g)</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>-2.7</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1287,75 +1287,75 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
       <c r="E11" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>16.4</v>
+        <v>10.6</v>
       </c>
       <c r="H11" t="n">
-        <v>18.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>18.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="K11" t="n">
-        <v>30.5</v>
+        <v>28.2</v>
       </c>
       <c r="L11" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="M11" t="n">
-        <v>47.6</v>
+        <v>39.2</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>-4.3</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8</v>
+        <v>-0.9</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>-9.199999999999999</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1365,79 +1365,75 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="E12" t="n">
-        <v>22.3</v>
+        <v>7.3</v>
       </c>
       <c r="F12" t="n">
-        <v>20.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>20.1</v>
+        <v>12.7</v>
       </c>
       <c r="I12" t="n">
-        <v>20.8</v>
+        <v>12.5</v>
       </c>
       <c r="J12" t="n">
-        <v>30.5</v>
+        <v>28.9</v>
       </c>
       <c r="K12" t="n">
-        <v>30.2</v>
+        <v>29.8</v>
       </c>
       <c r="L12" t="n">
-        <v>45.6</v>
+        <v>32.1</v>
       </c>
       <c r="M12" t="n">
-        <v>46.3</v>
+        <v>37.2</v>
       </c>
       <c r="N12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="O12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.6</v>
+        <v>-2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7</v>
+        <v>-5</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3</v>
+        <v>-0.9</v>
       </c>
       <c r="U12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>14.3 (3g)</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>-10.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1447,75 +1443,79 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3</v>
+        <v>14.7</v>
       </c>
       <c r="F13" t="n">
-        <v>17.6</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>21.2</v>
+        <v>15.6</v>
       </c>
       <c r="H13" t="n">
-        <v>19.9</v>
+        <v>14.2</v>
       </c>
       <c r="I13" t="n">
-        <v>19.9</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>27.8</v>
+        <v>28.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30.1</v>
+        <v>28.5</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6</v>
+        <v>55.4</v>
       </c>
       <c r="M13" t="n">
-        <v>42.8</v>
+        <v>46.6</v>
       </c>
       <c r="N13" t="n">
-        <v>10.3</v>
+        <v>5.4</v>
       </c>
       <c r="O13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3</v>
+        <v>-0.1</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13" t="n">
-        <v>21</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>19.3 (3g)</t>
+        </is>
+      </c>
       <c r="X13" t="n">
-        <v>-38</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1525,75 +1525,75 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>15.6</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>16.9</v>
       </c>
       <c r="H14" t="n">
-        <v>9.300000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I14" t="n">
-        <v>9.300000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="J14" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="K14" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="L14" t="n">
-        <v>43.9</v>
+        <v>39.9</v>
       </c>
       <c r="M14" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P14" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9</v>
+        <v>-1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14" t="n">
         <v>21</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>-13.4</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1607,55 +1607,55 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="E15" t="n">
-        <v>7.3</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>9.800000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="G15" t="n">
-        <v>10.6</v>
+        <v>20.6</v>
       </c>
       <c r="H15" t="n">
-        <v>12.7</v>
+        <v>19.9</v>
       </c>
       <c r="I15" t="n">
-        <v>12.5</v>
+        <v>17.1</v>
       </c>
       <c r="J15" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>29.8</v>
+        <v>25.3</v>
       </c>
       <c r="L15" t="n">
-        <v>32.1</v>
+        <v>43.6</v>
       </c>
       <c r="M15" t="n">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="N15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.7</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>-5</v>
+        <v>4.8</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9</v>
+        <v>3.7</v>
       </c>
       <c r="U15" t="n">
         <v>9</v>
@@ -1663,15 +1663,19 @@
       <c r="V15" t="n">
         <v>21</v>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>19.3 (3g)</t>
+        </is>
+      </c>
       <c r="X15" t="n">
-        <v>16.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1681,73 +1685,69 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E16" t="n">
-        <v>14.7</v>
+        <v>12.3</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>17.6</v>
       </c>
       <c r="G16" t="n">
-        <v>15.6</v>
+        <v>21.2</v>
       </c>
       <c r="H16" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="I16" t="n">
-        <v>14</v>
+        <v>19.9</v>
       </c>
       <c r="J16" t="n">
-        <v>28.4</v>
+        <v>27.8</v>
       </c>
       <c r="K16" t="n">
-        <v>28.5</v>
+        <v>30.1</v>
       </c>
       <c r="L16" t="n">
-        <v>55.4</v>
+        <v>41.6</v>
       </c>
       <c r="M16" t="n">
-        <v>46.6</v>
+        <v>42.8</v>
       </c>
       <c r="N16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q16" t="n">
         <v>5.4</v>
       </c>
-      <c r="O16" t="n">
-        <v>60</v>
-      </c>
-      <c r="P16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.5</v>
-      </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>8.699999999999999</v>
+        <v>-1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>22</v>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>19.3 (3g)</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>1.5</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="17">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E22" t="n">
         <v>18</v>
@@ -2205,10 +2205,10 @@
         <v>50</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="R22" t="n">
         <v>3.6</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="E28" t="n">
         <v>26</v>
@@ -2692,7 +2692,7 @@
         <v>65</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
         <v>-3.5</v>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="E32" t="n">
         <v>13</v>
@@ -3013,10 +3013,10 @@
         <v>60</v>
       </c>
       <c r="P32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="R32" t="n">
         <v>-1.3</v>
@@ -3127,7 +3127,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3141,55 +3141,55 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>12.3</v>
       </c>
       <c r="F34" t="n">
-        <v>5.6</v>
+        <v>11.8</v>
       </c>
       <c r="G34" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="H34" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>13.4</v>
       </c>
       <c r="J34" t="n">
-        <v>19.2</v>
+        <v>26.3</v>
       </c>
       <c r="K34" t="n">
-        <v>18.3</v>
+        <v>26</v>
       </c>
       <c r="L34" t="n">
-        <v>40.5</v>
+        <v>49.9</v>
       </c>
       <c r="M34" t="n">
-        <v>41.2</v>
+        <v>52.1</v>
       </c>
       <c r="N34" t="n">
         <v>4.7</v>
       </c>
       <c r="O34" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P34" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.7</v>
+        <v>-1.6</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.7</v>
+        <v>-2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="U34" t="n">
         <v>13</v>
@@ -3197,19 +3197,15 @@
       <c r="V34" t="n">
         <v>17</v>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>10.8 (4g)</t>
-        </is>
-      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>11</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3223,55 +3219,55 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="E35" t="n">
-        <v>12.3</v>
+        <v>15.7</v>
       </c>
       <c r="F35" t="n">
-        <v>11.8</v>
+        <v>18.6</v>
       </c>
       <c r="G35" t="n">
-        <v>13.5</v>
+        <v>16.8</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>16.9</v>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>17.3</v>
       </c>
       <c r="J35" t="n">
-        <v>26.3</v>
+        <v>24.7</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="L35" t="n">
-        <v>49.9</v>
+        <v>52.7</v>
       </c>
       <c r="M35" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="O35" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P35" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>-2.2</v>
+        <v>4.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3</v>
+        <v>-3.8</v>
       </c>
       <c r="U35" t="n">
         <v>13</v>
@@ -3279,15 +3275,19 @@
       <c r="V35" t="n">
         <v>17</v>
       </c>
-      <c r="W35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>21.0 (4g)</t>
+        </is>
+      </c>
       <c r="X35" t="n">
-        <v>-7.3</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3301,55 +3301,55 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="E36" t="n">
-        <v>15.7</v>
+        <v>11.7</v>
       </c>
       <c r="F36" t="n">
-        <v>18.6</v>
+        <v>9.4</v>
       </c>
       <c r="G36" t="n">
-        <v>16.8</v>
+        <v>7.4</v>
       </c>
       <c r="H36" t="n">
-        <v>16.9</v>
+        <v>10</v>
       </c>
       <c r="I36" t="n">
-        <v>17.3</v>
+        <v>10.4</v>
       </c>
       <c r="J36" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="K36" t="n">
-        <v>28.5</v>
+        <v>27.3</v>
       </c>
       <c r="L36" t="n">
-        <v>52.7</v>
+        <v>44.7</v>
       </c>
       <c r="M36" t="n">
-        <v>48.4</v>
+        <v>42.9</v>
       </c>
       <c r="N36" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="O36" t="n">
         <v>40</v>
       </c>
       <c r="P36" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1.2</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="T36" t="n">
-        <v>-3.8</v>
+        <v>-3.2</v>
       </c>
       <c r="U36" t="n">
         <v>13</v>
@@ -3359,17 +3359,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>21.0 (4g)</t>
+          <t>7.8 (5g)</t>
         </is>
       </c>
       <c r="X36" t="n">
-        <v>-6.3</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3383,55 +3383,55 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.5</v>
+        <v>30.5</v>
       </c>
       <c r="E37" t="n">
-        <v>11.7</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="N37" t="n">
         <v>9.4</v>
       </c>
-      <c r="G37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H37" t="n">
-        <v>10</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J37" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="M37" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5.1</v>
-      </c>
       <c r="O37" t="n">
+        <v>50</v>
+      </c>
+      <c r="P37" t="n">
         <v>40</v>
       </c>
-      <c r="P37" t="n">
-        <v>55</v>
-      </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="R37" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="S37" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="T37" t="n">
-        <v>-3.2</v>
+        <v>-0.2</v>
       </c>
       <c r="U37" t="n">
         <v>13</v>
@@ -3441,17 +3441,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>7.8 (5g)</t>
+          <t>33.5 (4g)</t>
         </is>
       </c>
       <c r="X37" t="n">
-        <v>-0.2</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3461,79 +3461,79 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.5</v>
+        <v>8.5</v>
       </c>
       <c r="E38" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
-        <v>31.4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="n">
-        <v>31.2</v>
+        <v>8.9</v>
       </c>
       <c r="H38" t="n">
-        <v>30.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>31.1</v>
+        <v>10.3</v>
       </c>
       <c r="J38" t="n">
-        <v>33.9</v>
+        <v>23.7</v>
       </c>
       <c r="K38" t="n">
-        <v>34.1</v>
+        <v>25.8</v>
       </c>
       <c r="L38" t="n">
-        <v>60.1</v>
+        <v>57</v>
       </c>
       <c r="M38" t="n">
-        <v>56.4</v>
+        <v>50.8</v>
       </c>
       <c r="N38" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P38" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3</v>
+        <v>-1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.2</v>
+        <v>-2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V38" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>33.5 (4g)</t>
+          <t>11.0 (4g)</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>-3.7</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3547,55 +3547,55 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.5</v>
+        <v>31.5</v>
       </c>
       <c r="E39" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>38.2</v>
       </c>
       <c r="G39" t="n">
-        <v>8.9</v>
+        <v>40.8</v>
       </c>
       <c r="H39" t="n">
-        <v>9.300000000000001</v>
+        <v>35.7</v>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>34.4</v>
       </c>
       <c r="J39" t="n">
-        <v>23.7</v>
+        <v>38.3</v>
       </c>
       <c r="K39" t="n">
-        <v>25.8</v>
+        <v>35.6</v>
       </c>
       <c r="L39" t="n">
-        <v>57</v>
+        <v>49.1</v>
       </c>
       <c r="M39" t="n">
-        <v>50.8</v>
+        <v>49</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="P39" t="n">
         <v>60</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.3</v>
+        <v>3.8</v>
       </c>
       <c r="S39" t="n">
-        <v>6.2</v>
+        <v>0.1</v>
       </c>
       <c r="T39" t="n">
-        <v>-2.1</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
         <v>8</v>
@@ -3605,17 +3605,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>11.0 (4g)</t>
+          <t>22.0 (4g)</t>
         </is>
       </c>
       <c r="X39" t="n">
-        <v>-2.2</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3629,55 +3629,55 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="E40" t="n">
-        <v>42</v>
+        <v>16.3</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2</v>
+        <v>16.8</v>
       </c>
       <c r="G40" t="n">
-        <v>40.8</v>
+        <v>18</v>
       </c>
       <c r="H40" t="n">
-        <v>35.7</v>
+        <v>18.9</v>
       </c>
       <c r="I40" t="n">
-        <v>34.4</v>
+        <v>19.3</v>
       </c>
       <c r="J40" t="n">
-        <v>38.3</v>
+        <v>35.4</v>
       </c>
       <c r="K40" t="n">
-        <v>35.6</v>
+        <v>33.8</v>
       </c>
       <c r="L40" t="n">
-        <v>49.1</v>
+        <v>54.4</v>
       </c>
       <c r="M40" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="N40" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="O40" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P40" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R40" t="n">
-        <v>3.8</v>
+        <v>-2.5</v>
       </c>
       <c r="S40" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="U40" t="n">
         <v>8</v>
@@ -3687,17 +3687,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>22.0 (4g)</t>
+          <t>20.2 (4g)</t>
         </is>
       </c>
       <c r="X40" t="n">
-        <v>-5.2</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3707,79 +3707,79 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="E41" t="n">
-        <v>16.3</v>
+        <v>21.3</v>
       </c>
       <c r="F41" t="n">
-        <v>16.8</v>
+        <v>22.6</v>
       </c>
       <c r="G41" t="n">
-        <v>18</v>
+        <v>21.8</v>
       </c>
       <c r="H41" t="n">
-        <v>18.9</v>
+        <v>20.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19.3</v>
+        <v>20.1</v>
       </c>
       <c r="J41" t="n">
-        <v>35.4</v>
+        <v>38.7</v>
       </c>
       <c r="K41" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="L41" t="n">
-        <v>54.4</v>
+        <v>43.9</v>
       </c>
       <c r="M41" t="n">
-        <v>51.6</v>
+        <v>46.9</v>
       </c>
       <c r="N41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O41" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P41" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.5</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="T41" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="U41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V41" t="n">
         <v>28</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>20.2 (4g)</t>
+          <t>16.8 (5g)</t>
         </is>
       </c>
       <c r="X41" t="n">
-        <v>-4.2</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3789,73 +3789,73 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E42" t="n">
-        <v>21.3</v>
+        <v>13</v>
       </c>
       <c r="F42" t="n">
-        <v>22.6</v>
+        <v>12.2</v>
       </c>
       <c r="G42" t="n">
-        <v>21.8</v>
+        <v>12.2</v>
       </c>
       <c r="H42" t="n">
-        <v>20.8</v>
+        <v>10.6</v>
       </c>
       <c r="I42" t="n">
-        <v>20.1</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
-        <v>38.7</v>
+        <v>28.2</v>
       </c>
       <c r="K42" t="n">
-        <v>33.4</v>
+        <v>25</v>
       </c>
       <c r="L42" t="n">
-        <v>43.9</v>
+        <v>75.3</v>
       </c>
       <c r="M42" t="n">
-        <v>46.9</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="O42" t="n">
         <v>50</v>
       </c>
       <c r="P42" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R42" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="S42" t="n">
-        <v>-2.9</v>
+        <v>10.8</v>
       </c>
       <c r="T42" t="n">
-        <v>5.3</v>
+        <v>3.2</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V42" t="n">
         <v>28</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>16.8 (5g)</t>
+          <t>8.7 (3g)</t>
         </is>
       </c>
       <c r="X42" t="n">
-        <v>-7.3</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="43">
@@ -4025,7 +4025,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4035,73 +4035,73 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="E45" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>12.2</v>
+        <v>5.6</v>
       </c>
       <c r="G45" t="n">
-        <v>12.2</v>
+        <v>5.8</v>
       </c>
       <c r="H45" t="n">
-        <v>10.6</v>
+        <v>6.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10.3</v>
+        <v>6.3</v>
       </c>
       <c r="J45" t="n">
-        <v>28.2</v>
+        <v>19.2</v>
       </c>
       <c r="K45" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
       <c r="L45" t="n">
-        <v>75.3</v>
+        <v>40.5</v>
       </c>
       <c r="M45" t="n">
-        <v>64.59999999999999</v>
+        <v>41.2</v>
       </c>
       <c r="N45" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
         <v>50</v>
       </c>
       <c r="P45" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R45" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.8</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U45" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V45" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>8.7 (3g)</t>
+          <t>10.8 (4g)</t>
         </is>
       </c>
       <c r="X45" t="n">
-        <v>-6.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="E46" t="n">
         <v>11</v>
@@ -4157,10 +4157,10 @@
         <v>60</v>
       </c>
       <c r="P46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="R46" t="n">
         <v>1.5</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="E53" t="n">
         <v>17</v>
@@ -4719,10 +4719,10 @@
         <v>60</v>
       </c>
       <c r="P53" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="R53" t="n">
         <v>0.2</v>
@@ -4907,12 +4907,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="E56" t="n">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="F56" t="n">
-        <v>18.2</v>
+        <v>9.6</v>
       </c>
       <c r="G56" t="n">
-        <v>17.3</v>
+        <v>13.7</v>
       </c>
       <c r="H56" t="n">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="I56" t="n">
-        <v>20.4</v>
+        <v>14.3</v>
       </c>
       <c r="J56" t="n">
-        <v>32</v>
+        <v>24.8</v>
       </c>
       <c r="K56" t="n">
-        <v>32.6</v>
+        <v>23.9</v>
       </c>
       <c r="L56" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="M56" t="n">
-        <v>45.4</v>
+        <v>39.7</v>
       </c>
       <c r="N56" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="O56" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P56" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="S56" t="n">
-        <v>-2.3</v>
+        <v>-5.5</v>
       </c>
       <c r="T56" t="n">
-        <v>-0.6</v>
+        <v>0.9</v>
       </c>
       <c r="U56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V56" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
-        <v>0.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4999,75 +4999,75 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="E57" t="n">
-        <v>7.7</v>
+        <v>22.3</v>
       </c>
       <c r="F57" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="G57" t="n">
-        <v>10</v>
+        <v>16.6</v>
       </c>
       <c r="H57" t="n">
-        <v>9.300000000000001</v>
+        <v>15.9</v>
       </c>
       <c r="I57" t="n">
-        <v>8.699999999999999</v>
+        <v>14.8</v>
       </c>
       <c r="J57" t="n">
-        <v>30.9</v>
+        <v>31.3</v>
       </c>
       <c r="K57" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="L57" t="n">
-        <v>40.5</v>
+        <v>46.9</v>
       </c>
       <c r="M57" t="n">
-        <v>36.7</v>
+        <v>52.2</v>
       </c>
       <c r="N57" t="n">
-        <v>3.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P57" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.8</v>
+        <v>0.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="S57" t="n">
-        <v>3.8</v>
+        <v>-5.3</v>
       </c>
       <c r="T57" t="n">
         <v>1.2</v>
       </c>
       <c r="U57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="V57" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>7.0 (5g)</t>
+          <t>5.7 (3g)</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>-3.4</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5084,72 +5084,68 @@
         <v>17.5</v>
       </c>
       <c r="E58" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
       <c r="G58" t="n">
-        <v>14.1</v>
+        <v>17.3</v>
       </c>
       <c r="H58" t="n">
-        <v>14.2</v>
+        <v>19.6</v>
       </c>
       <c r="I58" t="n">
-        <v>13.5</v>
+        <v>20.4</v>
       </c>
       <c r="J58" t="n">
-        <v>24.5</v>
+        <v>32</v>
       </c>
       <c r="K58" t="n">
-        <v>23.7</v>
+        <v>32.6</v>
       </c>
       <c r="L58" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M58" t="n">
-        <v>40.3</v>
+        <v>45.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
+        <v>70</v>
+      </c>
+      <c r="P58" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R58" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U58" t="n">
         <v>20</v>
       </c>
-      <c r="P58" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U58" t="n">
-        <v>23</v>
-      </c>
       <c r="V58" t="n">
-        <v>7</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>10.5 (4g)</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
-        <v>-6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5163,75 +5159,75 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
       <c r="E59" t="n">
-        <v>22.7</v>
+        <v>7.7</v>
       </c>
       <c r="F59" t="n">
-        <v>20.8</v>
+        <v>9.6</v>
       </c>
       <c r="G59" t="n">
-        <v>22.7</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>19.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>22.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>31.8</v>
+        <v>30.9</v>
       </c>
       <c r="K59" t="n">
-        <v>31.1</v>
+        <v>29.7</v>
       </c>
       <c r="L59" t="n">
-        <v>43.7</v>
+        <v>40.5</v>
       </c>
       <c r="M59" t="n">
-        <v>43.9</v>
+        <v>36.7</v>
       </c>
       <c r="N59" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="O59" t="n">
+        <v>70</v>
+      </c>
+      <c r="P59" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U59" t="n">
         <v>20</v>
       </c>
-      <c r="P59" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="R59" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="S59" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U59" t="n">
-        <v>22</v>
-      </c>
       <c r="V59" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>18.3 (7g)</t>
+          <t>7.0 (5g)</t>
         </is>
       </c>
       <c r="X59" t="n">
-        <v>-0.5</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5241,79 +5237,79 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
       <c r="E60" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>16.2</v>
       </c>
       <c r="G60" t="n">
-        <v>5.5</v>
+        <v>14.1</v>
       </c>
       <c r="H60" t="n">
-        <v>5.2</v>
+        <v>14.2</v>
       </c>
       <c r="I60" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="J60" t="n">
-        <v>22.5</v>
+        <v>24.5</v>
       </c>
       <c r="K60" t="n">
-        <v>21.1</v>
+        <v>23.7</v>
       </c>
       <c r="L60" t="n">
-        <v>48.6</v>
+        <v>41.2</v>
       </c>
       <c r="M60" t="n">
-        <v>53.8</v>
+        <v>40.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="O60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.3</v>
+        <v>-3</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.8</v>
+        <v>2.7</v>
       </c>
       <c r="S60" t="n">
-        <v>-5.2</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="U60" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="V60" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>4.1 (7g)</t>
+          <t>10.5 (4g)</t>
         </is>
       </c>
       <c r="X60" t="n">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5323,79 +5319,79 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
       <c r="E61" t="n">
-        <v>5.3</v>
+        <v>22.7</v>
       </c>
       <c r="F61" t="n">
-        <v>7.4</v>
+        <v>20.8</v>
       </c>
       <c r="G61" t="n">
-        <v>12.9</v>
+        <v>22.7</v>
       </c>
       <c r="H61" t="n">
-        <v>13.3</v>
+        <v>19.2</v>
       </c>
       <c r="I61" t="n">
-        <v>13.2</v>
+        <v>22.1</v>
       </c>
       <c r="J61" t="n">
-        <v>26.3</v>
+        <v>31.8</v>
       </c>
       <c r="K61" t="n">
-        <v>27</v>
+        <v>31.1</v>
       </c>
       <c r="L61" t="n">
-        <v>49</v>
+        <v>43.7</v>
       </c>
       <c r="M61" t="n">
-        <v>50.1</v>
+        <v>43.9</v>
       </c>
       <c r="N61" t="n">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="O61" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.3</v>
+        <v>-4.4</v>
       </c>
       <c r="R61" t="n">
-        <v>-5.8</v>
+        <v>-1.3</v>
       </c>
       <c r="S61" t="n">
-        <v>-1.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T61" t="n">
-        <v>-0.7</v>
+        <v>0.8</v>
       </c>
       <c r="U61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="V61" t="n">
         <v>7</v>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>7.4 (5g)</t>
+          <t>18.3 (7g)</t>
         </is>
       </c>
       <c r="X61" t="n">
-        <v>2.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5409,55 +5405,55 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="E62" t="n">
-        <v>12.3</v>
+        <v>5.7</v>
       </c>
       <c r="F62" t="n">
-        <v>10.2</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="H62" t="n">
-        <v>9.1</v>
+        <v>5.2</v>
       </c>
       <c r="I62" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J62" t="n">
-        <v>18.2</v>
+        <v>22.5</v>
       </c>
       <c r="K62" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="L62" t="n">
-        <v>38.4</v>
+        <v>48.6</v>
       </c>
       <c r="M62" t="n">
-        <v>42.2</v>
+        <v>53.8</v>
       </c>
       <c r="N62" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="O62" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P62" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4</v>
+        <v>-0.8</v>
       </c>
       <c r="S62" t="n">
-        <v>-3.8</v>
+        <v>-5.2</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.9</v>
+        <v>1.4</v>
       </c>
       <c r="U62" t="n">
         <v>28</v>
@@ -5465,15 +5461,19 @@
       <c r="V62" t="n">
         <v>18</v>
       </c>
-      <c r="W62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>4.1 (7g)</t>
+        </is>
+      </c>
       <c r="X62" t="n">
-        <v>14.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5483,79 +5483,79 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="E63" t="n">
-        <v>21.3</v>
+        <v>5.3</v>
       </c>
       <c r="F63" t="n">
-        <v>17.6</v>
+        <v>7.4</v>
       </c>
       <c r="G63" t="n">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="H63" t="n">
-        <v>16.6</v>
+        <v>13.3</v>
       </c>
       <c r="I63" t="n">
-        <v>16.6</v>
+        <v>13.2</v>
       </c>
       <c r="J63" t="n">
-        <v>28.6</v>
+        <v>26.3</v>
       </c>
       <c r="K63" t="n">
-        <v>28.9</v>
+        <v>27</v>
       </c>
       <c r="L63" t="n">
-        <v>40.7</v>
+        <v>49</v>
       </c>
       <c r="M63" t="n">
-        <v>45.7</v>
+        <v>50.1</v>
       </c>
       <c r="N63" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="O63" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="P63" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q63" t="n">
-        <v>-0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>-5.8</v>
       </c>
       <c r="S63" t="n">
-        <v>-5</v>
+        <v>-1.1</v>
       </c>
       <c r="T63" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="U63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V63" t="n">
         <v>7</v>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>9.7 (3g)</t>
+          <t>7.4 (5g)</t>
         </is>
       </c>
       <c r="X63" t="n">
-        <v>-2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5569,75 +5569,71 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="E64" t="n">
-        <v>4.7</v>
+        <v>12.3</v>
       </c>
       <c r="F64" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="G64" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="I64" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="K64" t="n">
-        <v>17.4</v>
+        <v>22.1</v>
       </c>
       <c r="L64" t="n">
-        <v>61.6</v>
+        <v>38.4</v>
       </c>
       <c r="M64" t="n">
-        <v>69.7</v>
+        <v>42.2</v>
       </c>
       <c r="N64" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O64" t="n">
         <v>60</v>
       </c>
       <c r="P64" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.2</v>
+        <v>0.4</v>
       </c>
       <c r="S64" t="n">
-        <v>-8.1</v>
+        <v>-3.8</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1</v>
+        <v>-3.9</v>
       </c>
       <c r="U64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V64" t="n">
-        <v>7</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>4.7 (3g)</t>
-        </is>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
-        <v>-7</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5647,75 +5643,79 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
       <c r="E65" t="n">
-        <v>17.7</v>
+        <v>21.3</v>
       </c>
       <c r="F65" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="G65" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="H65" t="n">
-        <v>20.6</v>
+        <v>16.6</v>
       </c>
       <c r="I65" t="n">
-        <v>22.8</v>
+        <v>16.6</v>
       </c>
       <c r="J65" t="n">
-        <v>35.8</v>
+        <v>28.6</v>
       </c>
       <c r="K65" t="n">
-        <v>35.6</v>
+        <v>28.9</v>
       </c>
       <c r="L65" t="n">
-        <v>44.6</v>
+        <v>40.7</v>
       </c>
       <c r="M65" t="n">
-        <v>44.8</v>
+        <v>45.7</v>
       </c>
       <c r="N65" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="O65" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.3</v>
+        <v>-0.9</v>
       </c>
       <c r="R65" t="n">
-        <v>-4.2</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
-        <v>-0.2</v>
+        <v>-5</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="U65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V65" t="n">
-        <v>18</v>
-      </c>
-      <c r="W65" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>9.7 (3g)</t>
+        </is>
+      </c>
       <c r="X65" t="n">
-        <v>5</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5725,79 +5725,79 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="E66" t="n">
-        <v>20.3</v>
+        <v>4.7</v>
       </c>
       <c r="F66" t="n">
-        <v>21.6</v>
+        <v>7.2</v>
       </c>
       <c r="G66" t="n">
-        <v>20.4</v>
+        <v>6.4</v>
       </c>
       <c r="H66" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="I66" t="n">
-        <v>20.1</v>
+        <v>7.4</v>
       </c>
       <c r="J66" t="n">
-        <v>30.9</v>
+        <v>17.5</v>
       </c>
       <c r="K66" t="n">
-        <v>30.2</v>
+        <v>17.4</v>
       </c>
       <c r="L66" t="n">
-        <v>71.59999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="M66" t="n">
-        <v>62.4</v>
+        <v>69.7</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O66" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.4</v>
+        <v>0.9</v>
       </c>
       <c r="R66" t="n">
-        <v>1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="S66" t="n">
-        <v>9.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="T66" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="U66" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="V66" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>21.7 (3g)</t>
+          <t>4.7 (3g)</t>
         </is>
       </c>
       <c r="X66" t="n">
-        <v>-14.6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5807,59 +5807,59 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="E67" t="n">
-        <v>12.7</v>
+        <v>17.7</v>
       </c>
       <c r="F67" t="n">
-        <v>13.4</v>
+        <v>18.6</v>
       </c>
       <c r="G67" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="H67" t="n">
-        <v>18.4</v>
+        <v>20.6</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>22.8</v>
       </c>
       <c r="J67" t="n">
-        <v>28.9</v>
+        <v>35.8</v>
       </c>
       <c r="K67" t="n">
-        <v>30.3</v>
+        <v>35.6</v>
       </c>
       <c r="L67" t="n">
-        <v>47.8</v>
+        <v>44.6</v>
       </c>
       <c r="M67" t="n">
-        <v>43.9</v>
+        <v>44.8</v>
       </c>
       <c r="N67" t="n">
-        <v>8.1</v>
+        <v>5.8</v>
       </c>
       <c r="O67" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P67" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>-4.6</v>
+        <v>-4.2</v>
       </c>
       <c r="S67" t="n">
-        <v>3.9</v>
+        <v>-0.2</v>
       </c>
       <c r="T67" t="n">
-        <v>-1.3</v>
+        <v>0.2</v>
       </c>
       <c r="U67" t="n">
         <v>20</v>
@@ -5869,13 +5869,13 @@
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5889,75 +5889,75 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
       <c r="E68" t="n">
-        <v>16</v>
+        <v>20.3</v>
       </c>
       <c r="F68" t="n">
-        <v>18.6</v>
+        <v>21.6</v>
       </c>
       <c r="G68" t="n">
-        <v>15.7</v>
+        <v>20.4</v>
       </c>
       <c r="H68" t="n">
-        <v>13.2</v>
+        <v>20.9</v>
       </c>
       <c r="I68" t="n">
-        <v>13.1</v>
+        <v>20.1</v>
       </c>
       <c r="J68" t="n">
         <v>30.9</v>
       </c>
       <c r="K68" t="n">
-        <v>31.8</v>
+        <v>30.2</v>
       </c>
       <c r="L68" t="n">
-        <v>53</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>44.2</v>
+        <v>62.4</v>
       </c>
       <c r="N68" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O68" t="n">
         <v>60</v>
       </c>
       <c r="P68" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q68" t="n">
         <v>-0.4</v>
       </c>
       <c r="R68" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="S68" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T68" t="n">
-        <v>-1</v>
+        <v>0.7</v>
       </c>
       <c r="U68" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>12.9 (7g)</t>
+          <t>21.7 (3g)</t>
         </is>
       </c>
       <c r="X68" t="n">
-        <v>7.1</v>
+        <v>-14.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5971,76 +5971,76 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
       <c r="E69" t="n">
-        <v>6.3</v>
+        <v>12.7</v>
       </c>
       <c r="F69" t="n">
-        <v>8.6</v>
+        <v>13.4</v>
       </c>
       <c r="G69" t="n">
-        <v>6.7</v>
+        <v>17.8</v>
       </c>
       <c r="H69" t="n">
-        <v>5.5</v>
+        <v>18.4</v>
       </c>
       <c r="I69" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>18.6</v>
+        <v>28.9</v>
       </c>
       <c r="K69" t="n">
-        <v>16.8</v>
+        <v>30.3</v>
       </c>
       <c r="L69" t="n">
-        <v>43.1</v>
+        <v>47.8</v>
       </c>
       <c r="M69" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="O69" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P69" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R69" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T69" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="U69" t="n">
         <v>20</v>
       </c>
-      <c r="Q69" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="R69" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S69" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U69" t="n">
-        <v>23</v>
-      </c>
       <c r="V69" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6049,80 +6049,80 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F70" t="n">
-        <v>15.6</v>
+        <v>18.6</v>
       </c>
       <c r="G70" t="n">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
       <c r="H70" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="I70" t="n">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="J70" t="n">
-        <v>23</v>
+        <v>30.9</v>
       </c>
       <c r="K70" t="n">
-        <v>22.1</v>
+        <v>31.8</v>
       </c>
       <c r="L70" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="M70" t="n">
-        <v>47.4</v>
+        <v>44.2</v>
       </c>
       <c r="N70" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O70" t="n">
+        <v>60</v>
+      </c>
+      <c r="P70" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="R70" t="n">
         <v>5.5</v>
       </c>
-      <c r="O70" t="n">
-        <v>70</v>
-      </c>
-      <c r="P70" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>3.3</v>
-      </c>
       <c r="S70" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T70" t="n">
-        <v>0.9</v>
+        <v>-1</v>
       </c>
       <c r="U70" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="V70" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>11.0 (6g)</t>
+          <t>12.9 (7g)</t>
         </is>
       </c>
       <c r="X70" t="n">
-        <v>-1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6131,75 +6131,71 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="G71" t="n">
-        <v>12.8</v>
+        <v>6.7</v>
       </c>
       <c r="H71" t="n">
-        <v>13.8</v>
+        <v>5.5</v>
       </c>
       <c r="I71" t="n">
-        <v>12.7</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
-        <v>29.6</v>
+        <v>18.6</v>
       </c>
       <c r="K71" t="n">
-        <v>28.9</v>
+        <v>16.8</v>
       </c>
       <c r="L71" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="M71" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="N71" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P71" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="R71" t="n">
-        <v>-1.7</v>
+        <v>2.4</v>
       </c>
       <c r="S71" t="n">
         <v>-0.8</v>
       </c>
       <c r="T71" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="U71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V71" t="n">
-        <v>26</v>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>13.0 (5g)</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
-        <v>-7.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6209,38 +6205,38 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>11.5</v>
       </c>
       <c r="E72" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="G72" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="H72" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="I72" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="J72" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K72" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="L72" t="n">
-        <v>56.4</v>
+        <v>52.8</v>
       </c>
       <c r="M72" t="n">
-        <v>55.5</v>
+        <v>47.4</v>
       </c>
       <c r="N72" t="n">
         <v>5.5</v>
@@ -6249,35 +6245,39 @@
         <v>70</v>
       </c>
       <c r="P72" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="R72" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="S72" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.9</v>
       </c>
-      <c r="T72" t="n">
-        <v>0.7</v>
-      </c>
       <c r="U72" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
         <v>26</v>
       </c>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>11.0 (6g)</t>
+        </is>
+      </c>
       <c r="X72" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6291,55 +6291,55 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="n">
         <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="G73" t="n">
-        <v>15.8</v>
+        <v>12.8</v>
       </c>
       <c r="H73" t="n">
-        <v>16.6</v>
+        <v>13.8</v>
       </c>
       <c r="I73" t="n">
-        <v>16.1</v>
+        <v>12.7</v>
       </c>
       <c r="J73" t="n">
-        <v>27.8</v>
+        <v>29.6</v>
       </c>
       <c r="K73" t="n">
         <v>28.9</v>
       </c>
       <c r="L73" t="n">
-        <v>47.5</v>
+        <v>43.4</v>
       </c>
       <c r="M73" t="n">
-        <v>50.3</v>
+        <v>44.2</v>
       </c>
       <c r="N73" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O73" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P73" t="n">
         <v>50</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="R73" t="n">
-        <v>-4.5</v>
+        <v>-1.7</v>
       </c>
       <c r="S73" t="n">
-        <v>-2.9</v>
+        <v>-0.8</v>
       </c>
       <c r="T73" t="n">
-        <v>-1.1</v>
+        <v>0.7</v>
       </c>
       <c r="U73" t="n">
         <v>20</v>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>24.2 (4g)</t>
+          <t>13.0 (5g)</t>
         </is>
       </c>
       <c r="X73" t="n">
-        <v>4</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6373,55 +6373,55 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="E74" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="F74" t="n">
-        <v>18.4</v>
+        <v>14.2</v>
       </c>
       <c r="G74" t="n">
-        <v>18.1</v>
+        <v>13.7</v>
       </c>
       <c r="H74" t="n">
-        <v>16.7</v>
+        <v>13.1</v>
       </c>
       <c r="I74" t="n">
-        <v>16.1</v>
+        <v>12.6</v>
       </c>
       <c r="J74" t="n">
-        <v>30.1</v>
+        <v>24</v>
       </c>
       <c r="K74" t="n">
-        <v>28.6</v>
+        <v>23.3</v>
       </c>
       <c r="L74" t="n">
-        <v>48.3</v>
+        <v>56.4</v>
       </c>
       <c r="M74" t="n">
-        <v>48.8</v>
+        <v>55.5</v>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="O74" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P74" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="R74" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="S74" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="T74" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="U74" t="n">
         <v>20</v>
@@ -6429,19 +6429,15 @@
       <c r="V74" t="n">
         <v>26</v>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>15.7 (6g)</t>
-        </is>
-      </c>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6451,79 +6447,79 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="E75" t="n">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="F75" t="n">
-        <v>8.6</v>
+        <v>11.6</v>
       </c>
       <c r="G75" t="n">
-        <v>8.699999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="H75" t="n">
-        <v>8.699999999999999</v>
+        <v>16.6</v>
       </c>
       <c r="I75" t="n">
-        <v>8.699999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="J75" t="n">
-        <v>21.5</v>
+        <v>27.8</v>
       </c>
       <c r="K75" t="n">
-        <v>22.7</v>
+        <v>28.9</v>
       </c>
       <c r="L75" t="n">
-        <v>44.6</v>
+        <v>47.5</v>
       </c>
       <c r="M75" t="n">
-        <v>46</v>
+        <v>50.3</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="O75" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P75" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="R75" t="n">
-        <v>-0.1</v>
+        <v>-4.5</v>
       </c>
       <c r="S75" t="n">
-        <v>-1.3</v>
+        <v>-2.9</v>
       </c>
       <c r="T75" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="U75" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="V75" t="n">
         <v>26</v>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>12.4 (5g)</t>
+          <t>24.2 (4g)</t>
         </is>
       </c>
       <c r="X75" t="n">
-        <v>13.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6537,75 +6533,75 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="E76" t="n">
-        <v>16.3</v>
+        <v>19.3</v>
       </c>
       <c r="F76" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="G76" t="n">
-        <v>20.9</v>
+        <v>18.1</v>
       </c>
       <c r="H76" t="n">
-        <v>19.5</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
-        <v>18.3</v>
+        <v>16.1</v>
       </c>
       <c r="J76" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="K76" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="L76" t="n">
-        <v>45</v>
+        <v>48.3</v>
       </c>
       <c r="M76" t="n">
-        <v>42.9</v>
+        <v>48.8</v>
       </c>
       <c r="N76" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O76" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="P76" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.7</v>
+        <v>2.3</v>
       </c>
       <c r="S76" t="n">
-        <v>2.1</v>
+        <v>-0.5</v>
       </c>
       <c r="T76" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="U76" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="V76" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>12.6 (5g)</t>
+          <t>15.7 (6g)</t>
         </is>
       </c>
       <c r="X76" t="n">
-        <v>-4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6619,75 +6615,75 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="E77" t="n">
-        <v>14.7</v>
+        <v>6.3</v>
       </c>
       <c r="F77" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="G77" t="n">
-        <v>12.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>14.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>14.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>26.1</v>
+        <v>21.5</v>
       </c>
       <c r="K77" t="n">
-        <v>28.4</v>
+        <v>22.7</v>
       </c>
       <c r="L77" t="n">
-        <v>46.3</v>
+        <v>44.6</v>
       </c>
       <c r="M77" t="n">
-        <v>56.2</v>
+        <v>46</v>
       </c>
       <c r="N77" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="O77" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P77" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="R77" t="n">
-        <v>-4.2</v>
+        <v>-0.1</v>
       </c>
       <c r="S77" t="n">
-        <v>-9.9</v>
+        <v>-1.3</v>
       </c>
       <c r="T77" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
       <c r="U77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V77" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>15.6 (5g)</t>
+          <t>12.4 (5g)</t>
         </is>
       </c>
       <c r="X77" t="n">
-        <v>-3.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6697,79 +6693,79 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="E78" t="n">
-        <v>13</v>
+        <v>16.3</v>
       </c>
       <c r="F78" t="n">
-        <v>11</v>
+        <v>17.6</v>
       </c>
       <c r="G78" t="n">
-        <v>11.2</v>
+        <v>20.9</v>
       </c>
       <c r="H78" t="n">
-        <v>11.7</v>
+        <v>19.5</v>
       </c>
       <c r="I78" t="n">
-        <v>10.3</v>
+        <v>18.3</v>
       </c>
       <c r="J78" t="n">
-        <v>27.1</v>
+        <v>29.9</v>
       </c>
       <c r="K78" t="n">
-        <v>26.1</v>
+        <v>29.6</v>
       </c>
       <c r="L78" t="n">
-        <v>45.9</v>
+        <v>45</v>
       </c>
       <c r="M78" t="n">
-        <v>44.8</v>
+        <v>42.9</v>
       </c>
       <c r="N78" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="O78" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P78" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="R78" t="n">
-        <v>0.7</v>
+        <v>-0.7</v>
       </c>
       <c r="S78" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="U78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V78" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>11.3 (6g)</t>
+          <t>12.6 (5g)</t>
         </is>
       </c>
       <c r="X78" t="n">
-        <v>2.9</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6779,79 +6775,79 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="E79" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="F79" t="n">
-        <v>15</v>
+        <v>10.4</v>
       </c>
       <c r="G79" t="n">
-        <v>10.5</v>
+        <v>12.4</v>
       </c>
       <c r="H79" t="n">
-        <v>11.1</v>
+        <v>14.1</v>
       </c>
       <c r="I79" t="n">
-        <v>10.5</v>
+        <v>14.6</v>
       </c>
       <c r="J79" t="n">
-        <v>28.3</v>
+        <v>26.1</v>
       </c>
       <c r="K79" t="n">
-        <v>27.1</v>
+        <v>28.4</v>
       </c>
       <c r="L79" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M79" t="n">
-        <v>45.6</v>
+        <v>56.2</v>
       </c>
       <c r="N79" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="O79" t="n">
         <v>50</v>
       </c>
       <c r="P79" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0</v>
+        <v>3.1</v>
       </c>
       <c r="R79" t="n">
-        <v>4.5</v>
+        <v>-4.2</v>
       </c>
       <c r="S79" t="n">
-        <v>0.1</v>
+        <v>-9.9</v>
       </c>
       <c r="T79" t="n">
-        <v>1.2</v>
+        <v>-2.4</v>
       </c>
       <c r="U79" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V79" t="n">
         <v>9</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>14.2 (4g)</t>
+          <t>15.6 (5g)</t>
         </is>
       </c>
       <c r="X79" t="n">
-        <v>4.3</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6861,79 +6857,79 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Forward</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
       <c r="E80" t="n">
-        <v>21.7</v>
+        <v>13</v>
       </c>
       <c r="F80" t="n">
-        <v>20.8</v>
+        <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>22.9</v>
+        <v>11.2</v>
       </c>
       <c r="H80" t="n">
-        <v>21.1</v>
+        <v>11.7</v>
       </c>
       <c r="I80" t="n">
-        <v>20.7</v>
+        <v>10.3</v>
       </c>
       <c r="J80" t="n">
-        <v>29.9</v>
+        <v>27.1</v>
       </c>
       <c r="K80" t="n">
-        <v>30.1</v>
+        <v>26.1</v>
       </c>
       <c r="L80" t="n">
-        <v>53.9</v>
+        <v>45.9</v>
       </c>
       <c r="M80" t="n">
-        <v>50.9</v>
+        <v>44.8</v>
       </c>
       <c r="N80" t="n">
-        <v>8.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="O80" t="n">
         <v>70</v>
       </c>
       <c r="P80" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="T80" t="n">
-        <v>-0.2</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V80" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>17.2 (4g)</t>
+          <t>11.3 (6g)</t>
         </is>
       </c>
       <c r="X80" t="n">
-        <v>-11</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6943,79 +6939,79 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Forward</t>
+          <t>Center</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24.5</v>
+        <v>10.5</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F81" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G81" t="n">
-        <v>27.5</v>
+        <v>10.5</v>
       </c>
       <c r="H81" t="n">
-        <v>25.8</v>
+        <v>11.1</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>10.5</v>
       </c>
       <c r="J81" t="n">
-        <v>29.1</v>
+        <v>28.3</v>
       </c>
       <c r="K81" t="n">
-        <v>29.7</v>
+        <v>27.1</v>
       </c>
       <c r="L81" t="n">
-        <v>51.6</v>
+        <v>45.7</v>
       </c>
       <c r="M81" t="n">
-        <v>50.2</v>
+        <v>45.6</v>
       </c>
       <c r="N81" t="n">
-        <v>8.9</v>
+        <v>6.4</v>
       </c>
       <c r="O81" t="n">
         <v>50</v>
       </c>
       <c r="P81" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.5</v>
+        <v>-0</v>
       </c>
       <c r="R81" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="S81" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="T81" t="n">
-        <v>-0.6</v>
+        <v>1.2</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="V81" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>24.4 (5g)</t>
+          <t>14.2 (4g)</t>
         </is>
       </c>
       <c r="X81" t="n">
-        <v>-3.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7029,55 +7025,55 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>21.7</v>
       </c>
       <c r="F82" t="n">
-        <v>4.4</v>
+        <v>20.8</v>
       </c>
       <c r="G82" t="n">
-        <v>5.4</v>
+        <v>22.9</v>
       </c>
       <c r="H82" t="n">
-        <v>6.2</v>
+        <v>21.1</v>
       </c>
       <c r="I82" t="n">
-        <v>6.7</v>
+        <v>20.7</v>
       </c>
       <c r="J82" t="n">
-        <v>26.1</v>
+        <v>29.9</v>
       </c>
       <c r="K82" t="n">
-        <v>27.5</v>
+        <v>30.1</v>
       </c>
       <c r="L82" t="n">
-        <v>40.6</v>
+        <v>53.9</v>
       </c>
       <c r="M82" t="n">
-        <v>47.3</v>
+        <v>50.9</v>
       </c>
       <c r="N82" t="n">
-        <v>3.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O82" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P82" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="R82" t="n">
-        <v>-2.3</v>
+        <v>0.1</v>
       </c>
       <c r="S82" t="n">
-        <v>-6.7</v>
+        <v>3</v>
       </c>
       <c r="T82" t="n">
-        <v>-1.5</v>
+        <v>-0.2</v>
       </c>
       <c r="U82" t="n">
         <v>8</v>
@@ -7087,17 +7083,17 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>7.4 (5g)</t>
+          <t>17.2 (4g)</t>
         </is>
       </c>
       <c r="X82" t="n">
-        <v>0.4</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7111,71 +7107,75 @@
         </is>
       </c>
       <c r="D83" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E83" t="n">
+        <v>35</v>
+      </c>
+      <c r="F83" t="n">
+        <v>30</v>
+      </c>
+      <c r="G83" t="n">
         <v>27.5</v>
       </c>
-      <c r="E83" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="F83" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G83" t="n">
-        <v>28.9</v>
-      </c>
       <c r="H83" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="I83" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>30.4</v>
+        <v>29.1</v>
       </c>
       <c r="K83" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="L83" t="n">
-        <v>53.6</v>
+        <v>51.6</v>
       </c>
       <c r="M83" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="N83" t="n">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="O83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R83" t="n">
-        <v>-2.7</v>
+        <v>5</v>
       </c>
       <c r="S83" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="T83" t="n">
-        <v>-0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="U83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V83" t="n">
-        <v>9</v>
-      </c>
-      <c r="W83" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>24.4 (5g)</t>
+        </is>
+      </c>
       <c r="X83" t="n">
-        <v>2.4</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7189,55 +7189,55 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8.5</v>
+        <v>27.5</v>
       </c>
       <c r="E84" t="n">
-        <v>6</v>
+        <v>23.7</v>
       </c>
       <c r="F84" t="n">
-        <v>5.4</v>
+        <v>25.2</v>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
+        <v>28.9</v>
       </c>
       <c r="H84" t="n">
-        <v>10.4</v>
+        <v>28.4</v>
       </c>
       <c r="I84" t="n">
-        <v>10.8</v>
+        <v>27.9</v>
       </c>
       <c r="J84" t="n">
-        <v>28.2</v>
+        <v>30.4</v>
       </c>
       <c r="K84" t="n">
-        <v>28.7</v>
+        <v>30.5</v>
       </c>
       <c r="L84" t="n">
-        <v>40</v>
+        <v>53.6</v>
       </c>
       <c r="M84" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="N84" t="n">
         <v>6.9</v>
       </c>
       <c r="O84" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="P84" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Q84" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R84" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="S84" t="n">
         <v>2.3</v>
       </c>
-      <c r="R84" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="S84" t="n">
-        <v>-10</v>
-      </c>
       <c r="T84" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="U84" t="n">
         <v>8</v>
@@ -7245,13 +7245,173 @@
       <c r="V84" t="n">
         <v>9</v>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Derrick Jones Jr.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Forward</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E85" t="n">
+        <v>6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I85" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J85" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K85" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L85" t="n">
+        <v>40</v>
+      </c>
+      <c r="M85" t="n">
+        <v>50</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O85" t="n">
+        <v>40</v>
+      </c>
+      <c r="P85" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R85" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-10</v>
+      </c>
+      <c r="T85" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>8</v>
+      </c>
+      <c r="V85" t="n">
+        <v>9</v>
+      </c>
+      <c r="W85" t="inlineStr">
         <is>
           <t>10.5 (6g)</t>
         </is>
       </c>
-      <c r="X84" t="n">
+      <c r="X85" t="n">
         <v>-14.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Guard</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G86" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="L86" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M86" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="N86" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O86" t="n">
+        <v>60</v>
+      </c>
+      <c r="P86" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R86" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="T86" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U86" t="n">
+        <v>8</v>
+      </c>
+      <c r="V86" t="n">
+        <v>9</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>7.4 (5g)</t>
+        </is>
+      </c>
+      <c r="X86" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -7265,7 +7425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="12" max="12"/>
@@ -7370,10 +7530,10 @@
         <v>0.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.909</v>
+        <v>2.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.826</v>
+        <v>1.417</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -7418,10 +7578,10 @@
         <v>0.9</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.385</v>
+        <v>1.435</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -7432,7 +7592,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -7451,36 +7611,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.623</v>
+        <v>0.574</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>23.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.806</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.926</v>
+        <v>1.345</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Allen's L30 average of 17.5 pts is 5.0 above the 12.5 line, supports the OVER. Opponent ranks as strong defense (#9) with slow pace (#21). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 16.0 pts (3.5 pts above line; 62% blended confidence).</t>
+          <t>Ball has a H2H avg of 26.3 pts vs this opponent (+5.8 vs line) — supporting the OVER. His H2H avg of 26.3 pts is 6.3 above his season L30; FG% trend +3.2% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). Mixed signal picture: 4/10 agree. Agreeing: Context, H2H, FG Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 23.1 pts (2.6 pts above line; 57% blended confidence). Risk: only 35% hit rate over L30 — line may be set fairly.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7499,36 +7659,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.6</v>
+        <v>0.717</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>23.2</v>
+        <v>33.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1.345</v>
+        <v>1.357</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Ball has a H2H avg of 26.3 pts vs this opponent (+6.8 vs line) — supporting the OVER. His H2H avg of 26.3 pts is 6.3 above his season L30; FG% trend +3.2% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Defense dissent. Projection model targets 23.2 pts (3.7 pts above line; 60% blended confidence).</t>
+          <t>Booker has a H2H avg of 33.0 pts vs this opponent (+7.5 vs line) — supporting the OVER. His H2H avg of 33.0 pts is 6.9 above his season L30; His TS% shifts +6.5% in this matchup. Opponent ranks as strong defense (#9) with slow pace (#21). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 33.5 pts (8.0 pts above line; 71% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7538,7 +7698,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7547,36 +7707,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.554</v>
+        <v>0.525</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>14.7</v>
+        <v>6.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.775</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.962</v>
+        <v>1.385</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Green has a H2H avg of 19.3 pts vs this opponent (+3.8 vs line) — working against the UNDER. His H2H avg of 19.3 pts is 2.2 above his season L30; FG% trend +4.8% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#21). Mixed signal picture: 2/10 agree. Agreeing: Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.7 pts (0.8 pts below line; 55% blended confidence). Risk: high scoring volatility (σ=8.2) introduces outcome uncertainty.</t>
+          <t>Kalkbrenner shows low scoring variance (σ=4.0) — highly predictable output. FG% trend +12.9% (L10 vs L30). Opponent ranks as below-average defense (#16) with slow pace (#22). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 6.1 pts (0.6 pts above line; 52% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7586,28 +7746,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.717</v>
+        <v>0.619</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>33.5</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
         <v>2.9</v>
@@ -7617,14 +7777,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Booker has a H2H avg of 33.0 pts vs this opponent (+7.5 vs line) — supporting the OVER. His H2H avg of 33.0 pts is 6.9 above his season L30; His TS% shifts +6.5% in this matchup. Opponent ranks as strong defense (#9) with slow pace (#21). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 33.5 pts (8.0 pts above line; 71% blended confidence). Risk: high scoring volatility (σ=7.9) introduces outcome uncertainty.</t>
+          <t>Diabaté shows low scoring variance (σ=4.9) — highly predictable output. Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — Context, Defense, Pace support under; Volume, HR L30 against. Projection model targets 2.7 pts (4.8 pts below line; 61% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7643,19 +7803,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.525</v>
+        <v>0.546</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1</v>
+        <v>14.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -7665,14 +7825,14 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Kalkbrenner shows low scoring variance (σ=4.0) — highly predictable output. FG% trend +12.9% (L10 vs L30). Opponent ranks as below-average defense (#16) with slow pace (#22). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 6.1 pts (0.6 pts above line; 52% blended confidence).</t>
+          <t>White has a H2H avg of 17.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. FG% trend +5.9% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 14.2 pts (0.7 pts above line; 54% blended confidence). Risk: minutes trending down (20.9 L10 vs 24.1 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7687,40 +7847,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.653</v>
+        <v>0.656</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>10.7</v>
       </c>
       <c r="I9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1.357</v>
+        <v>1.417</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Diabaté shows low scoring variance (σ=4.9) — highly predictable output. Opponent ranks as strong defense (#8) with slow pace (#22). 8/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 2.8 pts (5.7 pts below line; 65% blended confidence).</t>
+          <t>Knueppel shows recent scoring down 4.3 pts vs L30 (L5 vs L30 trend). FG% trend -4.4% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). 5/10 signals agree — Trend, Defense, Pace support under; Volume, HR L30 against. Projection model targets 10.7 pts (5.8 pts below line; 65% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7730,45 +7890,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.524</v>
+        <v>0.637</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K10" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] White has a H2H avg of 17.0 pts vs this opponent (+2.5 vs line) — supporting the lean OVER. FG% trend +5.9% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 14.2 pts (0.3 pts below line; 52% blended confidence). Risk: minutes trending down (20.9 L10 vs 24.1 L30 — role reduction would suppress counting stats.</t>
+          <t>Miller has a H2H avg of 14.3 pts vs this opponent (-5.2 vs line) — supporting the UNDER. His H2H avg of 14.3 pts is 6.5 below his season L30; His TS% shifts -10.9% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — Trend, Defense, H2H support under; Volume, HR L30 against. Projection model targets 13.8 pts (5.7 pts below line; 63% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7787,36 +7947,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.656</v>
+        <v>0.613</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>1.364</v>
+        <v>1.408</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Knueppel shows recent scoring down 4.3 pts vs L30 (L5 vs L30 trend). FG% trend -4.4% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#22). 5/10 signals agree — Trend, Defense, Pace support under; Volume, HR L30 against. Projection model targets 10.7 pts (5.8 pts below line; 65% blended confidence).</t>
+          <t>O'Neale's L30 average of 9.3 pts vs line of 7.5, works against the UNDER. FG% trend +4.7% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#21). Mixed signal picture: 3/10 agree. Agreeing: Defense, Pace, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 3.6 pts (3.9 pts below line; 61% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7826,7 +7986,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7835,36 +7995,36 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.637</v>
+        <v>0.694</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>13.8</v>
+        <v>18.3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Miller has a H2H avg of 14.3 pts vs this opponent (-5.2 vs line) — supporting the UNDER. His H2H avg of 14.3 pts is 6.5 below his season L30; His TS% shifts -10.9% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — Trend, Defense, H2H support under; Volume, HR L30 against. Projection model targets 13.8 pts (5.7 pts below line; 63% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Gillespie shows recent scoring down 2.7 pts vs L30 (L5 vs L30 trend). FG% trend -5.0% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#21). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, HR L10. Counter-signals: Trend, Defense, H2H. Projection model targets 18.3 pts (7.8 pts above line; 69% blended confidence). Risk: L3 has dropped to 7.3 (5.2 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7874,7 +8034,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7883,7 +8043,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.756</v>
+        <v>0.528</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -7892,27 +8052,27 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>14.1</v>
       </c>
       <c r="I13" t="n">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>1.435</v>
+        <v>1.385</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Brooks's L30 average of 19.9 pts is 5.4 above the 14.5 line, works against the UNDER. Opponent ranks as strong defense (#9) with slow pace (#21). 5/10 signals agree — Trend, Defense, Pace support under; Volume, HR L30 against. Projection model targets 3.2 pts (11.3 pts below line; 75% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
+          <t>Bridges has a H2H avg of 19.3 pts vs this opponent (+5.8 vs line) — supporting the OVER. His H2H avg of 19.3 pts is 5.3 above his season L30; FG% trend +8.7% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — Volume, HR L10, Context support over; HR L30, Trend against. Projection model targets 14.1 pts (0.6 pts above line; 52% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7922,7 +8082,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7931,36 +8091,36 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.613</v>
+        <v>0.623</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.917</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>1.82</v>
+        <v>1.345</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>O'Neale's L30 average of 9.3 pts vs line of 7.5, works against the UNDER. FG% trend +4.7% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#21). Mixed signal picture: 3/10 agree. Agreeing: Defense, Pace, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 3.6 pts (3.9 pts below line; 61% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Allen's L30 average of 17.5 pts is 5.0 above the 12.5 line, supports the OVER. Opponent ranks as strong defense (#9) with slow pace (#21). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 16.0 pts (3.5 pts above line; 62% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7970,7 +8130,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7979,36 +8139,36 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.694</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>18.3</v>
+        <v>14.7</v>
       </c>
       <c r="I15" t="n">
-        <v>7.8</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.385</v>
+        <v>1.364</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Gillespie shows recent scoring down 2.7 pts vs L30 (L5 vs L30 trend). FG% trend -5.0% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#21). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, HR L10. Counter-signals: Trend, Defense, H2H. Projection model targets 18.3 pts (7.8 pts above line; 69% blended confidence). Risk: L3 has dropped to 7.3 (5.2 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Green shows recent scoring up 3.1 pts vs L30 (L5 vs L30 trend). His H2H avg of 19.3 pts is 2.2 above his season L30; FG% trend +4.8% (L10 vs L30). Opponent ranks as strong defense (#9) with slow pace (#21). Mixed signal picture: 3/10 agree. Agreeing: Context, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.7 pts (1.8 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=8.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8018,7 +8178,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8027,7 +8187,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.528</v>
+        <v>0.756</v>
       </c>
       <c r="F16" t="n">
         <v>5</v>
@@ -8036,20 +8196,20 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14.1</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>11.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="K16" t="n">
-        <v>1.417</v>
+        <v>1.4</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Bridges has a H2H avg of 19.3 pts vs this opponent (+5.8 vs line) — supporting the OVER. His H2H avg of 19.3 pts is 5.3 above his season L30; FG% trend +8.7% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#22). 5/10 signals agree — Volume, HR L10, Context support over; HR L30, Trend against. Projection model targets 14.1 pts (0.6 pts above line; 52% blended confidence).</t>
+          <t>Brooks's L30 average of 19.9 pts is 5.4 above the 14.5 line, works against the UNDER. Opponent ranks as strong defense (#9) with slow pace (#21). 5/10 signals agree — Trend, Defense, Pace support under; Volume, HR L30 against. Projection model targets 3.2 pts (11.3 pts below line; 75% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8090,10 +8250,10 @@
         <v>6.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K17" t="n">
-        <v>1.357</v>
+        <v>1.408</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -8138,10 +8298,10 @@
         <v>0.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1.935</v>
+        <v>1.465</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -8186,10 +8346,10 @@
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
@@ -8234,10 +8394,10 @@
         <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="K20" t="n">
-        <v>1.417</v>
+        <v>1.385</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -8282,10 +8442,10 @@
         <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
@@ -8315,10 +8475,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.523</v>
+        <v>0.545</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -8327,17 +8487,17 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K22" t="n">
-        <v>1.408</v>
+        <v>1.435</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>DiVincenzo shows recent scoring up 3.6 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#4) with moderate pace (#19). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.8 pts (0.7 pts below line; 52% blended confidence). Risk: L3 has surged to 18.0 after a 3-pt performance (6.6 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>DiVincenzo shows recent scoring up 3.6 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#4) with moderate pace (#19). 7/10 signals agree (Volume, HR L30, Context, Defense among the strongest); HR L10, Trend dissent. Projection model targets 9.8 pts (1.7 pts below line; 54% blended confidence). Risk: L3 has surged to 18.0 after a 3-pt performance (6.6 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -8474,10 +8634,10 @@
         <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>1.98</v>
+        <v>1.901</v>
       </c>
       <c r="K25" t="n">
-        <v>1.787</v>
+        <v>1.833</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -8522,10 +8682,10 @@
         <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.03</v>
+        <v>1.385</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
@@ -8570,10 +8730,10 @@
         <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
@@ -8603,7 +8763,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.718</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
@@ -8615,7 +8775,7 @@
         <v>34.8</v>
       </c>
       <c r="I28" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -8625,7 +8785,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Edwards shows recent scoring down 3.5 pts vs L30 (L5 vs L30 trend). Opponent ranks as elite defense (#4) with moderate pace (#19). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 34.8 pts (8.3 pts above line; 68% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
+          <t>Edwards's L30 average of 29.1 pts is 3.6 above the 25.5 line, supports the OVER. Opponent ranks as elite defense (#4) with moderate pace (#19). Mixed signal picture: 4/10 agree. Agreeing: Volume, HR L30, Context. Counter-signals: HR L10, Trend, Defense. Projection model targets 34.8 pts (9.3 pts above line; 71% blended confidence). Risk: high scoring volatility (σ=10.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
@@ -8666,10 +8826,10 @@
         <v>0.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.357</v>
+        <v>1.345</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -8791,33 +8951,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.529</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>13.4</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Holmgren has a H2H avg of 12.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 12.0 pts is 4.1 below his season L30. Opponent ranks as strong defense (#6) with moderate pace (#17). 5/10 signals agree — Trend, Defense, H2H support under; Volume, HR L30 against. Projection model targets 13.4 pts (1.1 pts below line; 52% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Holmgren has a H2H avg of 12.0 pts vs this opponent (-3.5 vs line) — supporting the UNDER. His H2H avg of 12.0 pts is 4.1 below his season L30. Opponent ranks as strong defense (#6) with moderate pace (#17). 6/10 signals agree — Trend, Context, Defense support under; Volume, HR L30 against. Projection model targets 13.4 pts (2.1 pts below line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -8858,10 +9018,10 @@
         <v>2.2</v>
       </c>
       <c r="J33" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K33" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
@@ -8872,7 +9032,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8882,7 +9042,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -8891,7 +9051,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.644</v>
+        <v>0.573</v>
       </c>
       <c r="F34" t="n">
         <v>5</v>
@@ -8900,27 +9060,27 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>1.746</v>
+        <v>1.364</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Caruso has a H2H avg of 10.8 pts vs this opponent (+6.3 vs line) — supporting the OVER. His H2H avg of 10.8 pts is 4.5 above his season L30; His TS% shifts +11.0% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 9.8 pts (5.3 pts above line; 64% blended confidence).</t>
+          <t>Mitchell shows low scoring variance (σ=4.7) — highly predictable output. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Trend, Context, Defense support under; Volume, HR L30 against. Projection model targets 9.7 pts (2.8 pts below line; 57% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8935,40 +9095,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.573</v>
+        <v>0.581</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9.699999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="K35" t="n">
-        <v>1.385</v>
+        <v>1.4</v>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Mitchell shows low scoring variance (σ=4.7) — highly predictable output. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Trend, Context, Defense support under; Volume, HR L30 against. Projection model targets 9.7 pts (2.8 pts below line; 57% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Williams has a H2H avg of 21.0 pts vs this opponent (+2.5 vs line) — working against the UNDER. His H2H avg of 21.0 pts is 3.7 above his season L30; His TS% shifts -6.3% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 15.6 pts (2.9 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.4) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8978,45 +9138,45 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.581</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>15.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="K36" t="n">
-        <v>1.385</v>
+        <v>1.435</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Williams has a H2H avg of 21.0 pts vs this opponent (+2.5 vs line) — working against the UNDER. His H2H avg of 21.0 pts is 3.7 above his season L30; His TS% shifts -6.3% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 15.6 pts (2.9 pts below line; 58% blended confidence). Risk: high scoring volatility (σ=7.4) introduces outcome uncertainty.</t>
+          <t>Wallace's L30 average of 10.4 pts is 3.9 above the 6.5 line, supports the OVER. His H2H avg of 7.8 pts is 2.6 below his season L30. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 8.3 pts (1.8 pts above line; 56% blended confidence). Risk: minutes trending down (24.1 L10 vs 27.3 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9035,7 +9195,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.512</v>
       </c>
       <c r="F37" t="n">
         <v>5</v>
@@ -9044,27 +9204,27 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>8.300000000000001</v>
+        <v>31.2</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>1.408</v>
+        <v>1.364</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Wallace's L30 average of 10.4 pts is 3.9 above the 6.5 line, supports the OVER. His H2H avg of 7.8 pts is 2.6 below his season L30. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 8.3 pts (1.8 pts above line; 56% blended confidence). Risk: minutes trending down (24.1 L10 vs 27.3 L30 — role reduction would suppress counting stats.</t>
+          <t>Gilgeous-Alexander has a H2H avg of 33.5 pts vs this opponent (+3.0 vs line) — supporting the OVER. His H2H avg of 33.5 pts is 2.4 above his season L30; His TS% shifts -3.7% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, Trend, Context support over; HR L30, HR L10 against. Projection model targets 31.2 pts (0.7 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=9.4) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9074,45 +9234,45 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.512</v>
+        <v>0.502</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>31.2</v>
+        <v>8.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="K38" t="n">
-        <v>1.385</v>
+        <v>1.465</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Gilgeous-Alexander has a H2H avg of 33.5 pts vs this opponent (+3.0 vs line) — supporting the OVER. His H2H avg of 33.5 pts is 2.4 above his season L30; His TS% shifts -3.7% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, Trend, Context support over; HR L30, HR L10 against. Projection model targets 31.2 pts (0.7 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=9.4) introduces outcome uncertainty.</t>
+          <t>[Low conviction — lean only] Hachimura has a H2H avg of 11.0 pts vs this opponent (+2.5 vs line) — supporting the lean OVER. FG% trend +6.2% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 8.5 pts (0.0 pts below line; 50% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9122,7 +9282,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9131,36 +9291,36 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.547</v>
+        <v>0.744</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>8.5</v>
+        <v>22.2</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="K39" t="n">
-        <v>1.417</v>
+        <v>1.357</v>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Hachimura has a H2H avg of 11.0 pts vs this opponent (+3.5 vs line) — supporting the OVER. FG% trend +6.2% (L10 vs L30). Opponent ranks as strong defense (#8) with slow pace (#28). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 8.5 pts (1.0 pts above line; 54% blended confidence).</t>
+          <t>Dončić has a H2H avg of 22.0 pts vs this opponent (-9.5 vs line) — supporting the UNDER. His H2H avg of 22.0 pts is 12.4 below his season L30; His TS% shifts -5.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 3/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 22.2 pts (9.3 pts below line; 74% blended confidence). Risk: L3 has surged to 42.0 after a 25-pt performance (7.6 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9179,7 +9339,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.748</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="F40" t="n">
         <v>3</v>
@@ -9188,27 +9348,27 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>22.2</v>
+        <v>15.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="K40" t="n">
-        <v>1.4</v>
+        <v>1.385</v>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Dončić has a H2H avg of 22.0 pts vs this opponent (-10.5 vs line) — supporting the UNDER. His H2H avg of 22.0 pts is 12.4 below his season L30; His TS% shifts -5.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 3/10 agree. Agreeing: Defense, H2H, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 22.2 pts (10.3 pts below line; 74% blended confidence). Risk: L3 has surged to 42.0 after a 25-pt performance (7.6 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>James shows recent scoring down 2.5 pts vs L30 (L5 vs L30 trend). His TS% shifts -4.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 15.2 pts (2.3 pts below line; 56% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9223,40 +9383,40 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.555</v>
+        <v>0.6</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K41" t="n">
-        <v>1.385</v>
+        <v>1.345</v>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>James has a H2H avg of 20.2 pts vs this opponent (+3.7 vs line) — working against the UNDER. His TS% shifts -4.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 15.2 pts (1.3 pts below line; 55% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Reaves has a H2H avg of 16.8 pts vs this opponent (-2.7 vs line) — supporting the UNDER. His H2H avg of 16.8 pts is 3.3 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as strong defense (#6) with slow pace (#28). 6/10 signals agree — HR L30, Context, Defense support under; Volume, HR L10 against. Projection model targets 15.5 pts (4.0 pts below line; 59% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -9271,23 +9431,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.6</v>
+        <v>0.586</v>
       </c>
       <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
         <v>6</v>
       </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
-        <v>15.5</v>
-      </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.05</v>
@@ -9297,7 +9457,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>Reaves has a H2H avg of 16.8 pts vs this opponent (-2.7 vs line) — supporting the UNDER. His H2H avg of 16.8 pts is 3.3 below his season L30; His TS% shifts -7.3% in this matchup. Opponent ranks as strong defense (#6) with slow pace (#28). 6/10 signals agree — HR L30, Context, Defense support under; Volume, HR L10 against. Projection model targets 15.5 pts (4.0 pts below line; 59% blended confidence).</t>
+          <t>Ayton's L30 average of 10.3 pts vs line of 9.5, works against the UNDER. His H2H avg of 8.7 pts is 1.6 below his season L30; His TS% shifts -6.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 6.0 pts (3.5 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9338,10 +9498,10 @@
         <v>1.7</v>
       </c>
       <c r="J43" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="K43" t="n">
-        <v>1.435</v>
+        <v>1.645</v>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
@@ -9386,10 +9546,10 @@
         <v>1.8</v>
       </c>
       <c r="J44" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="K44" t="n">
-        <v>1.435</v>
+        <v>1.465</v>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
@@ -9400,7 +9560,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9410,7 +9570,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9419,29 +9579,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.586</v>
+        <v>0.644</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J45" t="n">
-        <v>3.05</v>
+        <v>1.725</v>
       </c>
       <c r="K45" t="n">
-        <v>1.357</v>
+        <v>2.05</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Ayton's L30 average of 10.3 pts vs line of 9.5, works against the UNDER. His H2H avg of 8.7 pts is 1.6 below his season L30; His TS% shifts -6.2% in this matchup. Opponent ranks as strong defense (#8) with slow pace (#28). Mixed signal picture: 4/10 agree. Agreeing: Context, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 6.0 pts (3.5 pts below line; 58% blended confidence).</t>
+          <t>Caruso has a H2H avg of 10.8 pts vs this opponent (+6.3 vs line) — supporting the OVER. His H2H avg of 10.8 pts is 4.5 above his season L30; His TS% shifts +11.0% in this matchup. Opponent ranks as average defense (#13) with moderate pace (#17). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 9.8 pts (5.3 pts above line; 64% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9467,29 +9627,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.614</v>
+        <v>0.625</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I46" t="n">
         <v>4.7</v>
       </c>
-      <c r="I46" t="n">
-        <v>3.8</v>
-      </c>
       <c r="J46" t="n">
-        <v>1.901</v>
+        <v>2.8</v>
       </c>
       <c r="K46" t="n">
-        <v>1.862</v>
+        <v>1.408</v>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>Green shows low scoring variance (σ=4.6) — highly predictable output. FG% trend +5.7% (L10 vs L30). Opponent ranks as below-average defense (#16) with above-average pace (#10). Mixed signal picture: 1/10 agree. Agreeing: Context. Counter-signals: Volume, HR L30, HR L10. Projection model targets 4.7 pts (3.8 pts below line; 61% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Green shows low scoring variance (σ=4.6) — highly predictable output. FG% trend +5.7% (L10 vs L30). Opponent ranks as below-average defense (#16) with above-average pace (#10). Mixed signal picture: 2/10 agree. Agreeing: Volume, Context. Counter-signals: HR L30, HR L10, Trend. Projection model targets 4.8 pts (4.7 pts below line; 62% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -9530,10 +9690,10 @@
         <v>5.3</v>
       </c>
       <c r="J47" t="n">
-        <v>1.917</v>
+        <v>3.05</v>
       </c>
       <c r="K47" t="n">
-        <v>1.84</v>
+        <v>1.357</v>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
@@ -9578,10 +9738,10 @@
         <v>0.1</v>
       </c>
       <c r="J48" t="n">
-        <v>1.917</v>
+        <v>2.9</v>
       </c>
       <c r="K48" t="n">
-        <v>1.84</v>
+        <v>1.385</v>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
@@ -9626,10 +9786,10 @@
         <v>5.6</v>
       </c>
       <c r="J49" t="n">
-        <v>1.862</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>1.901</v>
+        <v>1.364</v>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
@@ -9674,10 +9834,10 @@
         <v>2.5</v>
       </c>
       <c r="J50" t="n">
-        <v>1.813</v>
+        <v>2.6</v>
       </c>
       <c r="K50" t="n">
-        <v>1.952</v>
+        <v>1.465</v>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
@@ -9722,10 +9882,10 @@
         <v>4.2</v>
       </c>
       <c r="J51" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K51" t="n">
-        <v>1.877</v>
+        <v>1.385</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
@@ -9770,10 +9930,10 @@
         <v>0.7</v>
       </c>
       <c r="J52" t="n">
-        <v>1.877</v>
+        <v>3.1</v>
       </c>
       <c r="K52" t="n">
-        <v>1.877</v>
+        <v>1.345</v>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
@@ -9803,29 +9963,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.637</v>
+        <v>0.623</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="J53" t="n">
-        <v>1.813</v>
+        <v>3.05</v>
       </c>
       <c r="K53" t="n">
-        <v>1.952</v>
+        <v>1.357</v>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>Strus's L30 average of 11.0 pts vs line of 10.5, works against the UNDER. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 3/10 agree. Agreeing: HR L30, Context, Min Trend. Counter-signals: Volume, HR L10, Trend. Projection model targets 4.7 pts (5.8 pts below line; 63% blended confidence). Risk: L3 has surged to 17.0 after a 10-pt performance (6.0 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Strus's L30 average of 11.0 pts vs line of 9.5, works against the UNDER. Opponent ranks as below-average defense (#16) with above-average pace (#12). Mixed signal picture: 1/10 agree. Agreeing: Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 4.6 pts (4.9 pts below line; 62% blended confidence). Risk: L3 has surged to 17.0 after a 10-pt performance (6.0 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
@@ -9866,10 +10026,10 @@
         <v>0.7</v>
       </c>
       <c r="J54" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="K54" t="n">
-        <v>1.787</v>
+        <v>1.345</v>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
@@ -9914,10 +10074,10 @@
         <v>3.8</v>
       </c>
       <c r="J55" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="K55" t="n">
-        <v>1.787</v>
+        <v>1.417</v>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
@@ -9928,17 +10088,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9947,84 +10107,84 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.636</v>
+        <v>0.57</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>21.9</v>
+        <v>10.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
-        <v>1.893</v>
+        <v>1.877</v>
       </c>
       <c r="K56" t="n">
-        <v>1.826</v>
+        <v>1.877</v>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Bey shows recent scoring down 2.2 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#20) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 21.9 pts (4.4 pts above line; 63% blended confidence).</t>
+          <t>Melton shows recent scoring down 4.7 pts vs L30 (L5 vs L30 trend). FG% trend -5.5% (L10 vs L30). Opponent ranks as average defense (#12) with above-average pace (#10). Mixed signal picture: 4/10 agree. Agreeing: Trend, Context, Defense. Counter-signals: Volume, HR L30, HR L10. Projection model targets 10.5 pts (3.0 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=9.6) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.581</v>
+        <v>0.501</v>
       </c>
       <c r="F57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>6.5</v>
+        <v>14.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1.917</v>
       </c>
       <c r="K57" t="n">
-        <v>1.746</v>
+        <v>1.84</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Jones has a H2H avg of 7.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 7.0 pts is 1.7 below his season L30; His TS% shifts -3.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 6.5 pts (3.0 pts below line; 58% blended confidence).</t>
+          <t>[Low conviction — lean only] Santos has a H2H avg of 5.7 pts vs this opponent (-8.8 vs line) — working against the lean OVER. His H2H avg of 5.7 pts is 9.1 below his season L30; His TS% shifts +6.4% in this matchup. Opponent ranks as below-average defense (#16) with above-average pace (#10). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); H2H, FG Trend dissent. Projection model targets 14.3 pts (0.2 pts below line; 50% blended confidence). Risk: high scoring volatility (σ=8.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10034,7 +10194,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -10043,7 +10203,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.662</v>
+        <v>0.636</v>
       </c>
       <c r="F58" t="n">
         <v>5</v>
@@ -10052,27 +10212,27 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>12.1</v>
+        <v>21.9</v>
       </c>
       <c r="I58" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
-        <v>2.01</v>
+        <v>3.05</v>
       </c>
       <c r="K58" t="n">
-        <v>1.746</v>
+        <v>1.357</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>Henderson has a H2H avg of 10.5 pts vs this opponent (-7.0 vs line) — supporting the UNDER. His H2H avg of 10.5 pts is 3.0 below his season L30; His TS% shifts -6.0% in this matchup. Opponent ranks as weak defense (#23) with above-average pace (#7). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 12.1 pts (5.4 pts below line; 66% blended confidence).</t>
+          <t>Bey shows recent scoring down 2.2 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#20) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 21.9 pts (4.4 pts above line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10087,40 +10247,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>T1_PREMIUM</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.701</v>
+        <v>0.581</v>
       </c>
       <c r="F59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>20.6</v>
+        <v>6.5</v>
       </c>
       <c r="I59" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>1.847</v>
+        <v>2.65</v>
       </c>
       <c r="K59" t="n">
-        <v>1.885</v>
+        <v>1.455</v>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Avdija has a H2H avg of 18.3 pts vs this opponent (-8.2 vs line) — supporting the UNDER. His H2H avg of 18.3 pts is 3.8 below his season L30. Opponent ranks as below-average defense (#22) with above-average pace (#7). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 20.6 pts (5.9 pts below line; 70% blended confidence).</t>
+          <t>Jones has a H2H avg of 7.0 pts vs this opponent (-2.5 vs line) — supporting the UNDER. His H2H avg of 7.0 pts is 1.7 below his season L30; His TS% shifts -3.4% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, H2H. Counter-signals: HR L30, HR L10, Trend. Projection model targets 6.5 pts (3.0 pts below line; 58% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10139,36 +10299,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.541</v>
+        <v>0.631</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>4.3</v>
+        <v>12.1</v>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J60" t="n">
-        <v>1.758</v>
+        <v>2.65</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>1.455</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Missi shows low scoring variance (σ=2.8) — highly predictable output. His H2H avg of 4.1 pts is 1.7 below his season L30; FG% trend -5.2% (L10 vs L30). Opponent ranks as weak defense (#28) with moderate pace (#18). 6/10 signals agree — HR L30, Trend, Context support under; Volume, HR L10 against. Projection model targets 4.3 pts (1.2 pts below line; 54% blended confidence).</t>
+          <t>Henderson has a H2H avg of 10.5 pts vs this opponent (-6.0 vs line) — supporting the UNDER. His H2H avg of 10.5 pts is 3.0 below his season L30; His TS% shifts -6.0% in this matchup. Opponent ranks as weak defense (#23) with above-average pace (#7). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 12.1 pts (4.4 pts below line; 63% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10183,40 +10343,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_PREMIUM</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.579</v>
+        <v>0.701</v>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
-        <v>10.3</v>
+        <v>20.6</v>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="J61" t="n">
-        <v>1.855</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>1.87</v>
+        <v>1.364</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Clingan has a H2H avg of 7.4 pts vs this opponent (-6.1 vs line) — supporting the UNDER. His H2H avg of 7.4 pts is 5.8 below his season L30. Opponent ranks as weak defense (#25) with above-average pace (#7). 6/10 signals agree — Volume, Trend, Context support under; HR L30, HR L10 against. Projection model targets 10.3 pts (3.2 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
+          <t>Avdija has a H2H avg of 18.3 pts vs this opponent (-8.2 vs line) — supporting the UNDER. His H2H avg of 18.3 pts is 3.8 below his season L30. Opponent ranks as below-average defense (#22) with above-average pace (#7). 7/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 20.6 pts (5.9 pts below line; 70% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10226,45 +10386,45 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.754</v>
+        <v>0.541</v>
       </c>
       <c r="F62" t="n">
         <v>6</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>18.3</v>
+        <v>4.3</v>
       </c>
       <c r="I62" t="n">
-        <v>9.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
-        <v>1.833</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>1.893</v>
+        <v>1.364</v>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Queen shows low scoring variance (σ=4.8) — highly predictable output. FG% trend -3.8% (L10 vs L30). Opponent ranks as weak defense (#28) with moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10 support over; H2H, Pace against. Projection model targets 18.3 pts (9.8 pts above line; 75% blended confidence). Risk: minutes trending down (18.2 L10 vs 22.1 L30 — role reduction would suppress counting stats.</t>
+          <t>Missi shows low scoring variance (σ=2.8) — highly predictable output. His H2H avg of 4.1 pts is 1.7 below his season L30; FG% trend -5.2% (L10 vs L30). Opponent ranks as weak defense (#28) with moderate pace (#18). 6/10 signals agree — HR L30, Trend, Context support under; Volume, HR L10 against. Projection model targets 4.3 pts (1.2 pts below line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10283,36 +10443,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.644</v>
+        <v>0.579</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>12.4</v>
+        <v>10.3</v>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J63" t="n">
-        <v>1.952</v>
+        <v>2.9</v>
       </c>
       <c r="K63" t="n">
-        <v>1.8</v>
+        <v>1.385</v>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>Holiday has a H2H avg of 9.7 pts vs this opponent (-7.8 vs line) — supporting the UNDER. His H2H avg of 9.7 pts is 6.9 below his season L30; FG% trend -5.0% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Defense dissent. Projection model targets 12.4 pts (5.1 pts below line; 64% blended confidence). Risk: L3 has surged to 21.3 after a 6-pt performance (4.7 above L30) — if that momentum carries, this under is at risk.</t>
+          <t>Clingan has a H2H avg of 7.4 pts vs this opponent (-6.1 vs line) — supporting the UNDER. His H2H avg of 7.4 pts is 5.8 below his season L30. Opponent ranks as weak defense (#25) with above-average pace (#7). 6/10 signals agree — Volume, Trend, Context support under; HR L30, HR L10 against. Projection model targets 10.3 pts (3.2 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.7) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10322,45 +10482,45 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>T3_LEAN</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.537</v>
+        <v>0.754</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>5.2</v>
+        <v>18.3</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J64" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="K64" t="n">
-        <v>1.943</v>
+        <v>1.417</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] III shows low scoring variance (σ=4.4) — highly predictable output. His H2H avg of 4.7 pts is 2.7 below his season L30; His TS% shifts -7.0% in this matchup. Opponent ranks as weak defense (#25) with above-average pace (#7). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, H2H dissent. Projection model targets 5.2 pts (0.3 pts below line; 53% blended confidence).</t>
+          <t>Queen shows low scoring variance (σ=4.8) — highly predictable output. FG% trend -3.8% (L10 vs L30). Opponent ranks as weak defense (#28) with moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10 support over; H2H, Pace against. Projection model targets 18.3 pts (9.8 pts above line; 75% blended confidence). Risk: minutes trending down (18.2 L10 vs 22.1 L30 — role reduction would suppress counting stats.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10370,7 +10530,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10379,36 +10539,36 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.602</v>
+        <v>0.644</v>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>24.1</v>
+        <v>12.4</v>
       </c>
       <c r="I65" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
-        <v>1.787</v>
+        <v>1.87</v>
       </c>
       <c r="K65" t="n">
-        <v>1.943</v>
+        <v>1.87</v>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>III shows recent scoring down 4.2 pts vs L30 (L5 vs L30 trend). Opponent ranks as below-average defense (#20) with moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 24.1 pts (3.6 pts above line; 60% blended confidence). Risk: L3 has dropped to 17.7 (5.1 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Holiday has a H2H avg of 9.7 pts vs this opponent (-7.8 vs line) — supporting the UNDER. His H2H avg of 9.7 pts is 6.9 below his season L30; FG% trend -5.0% (L10 vs L30). Opponent ranks as weak defense (#23) with above-average pace (#7). 7/10 signals agree (Volume, HR L30, HR L10, Context among the strongest); Trend, Defense dissent. Projection model targets 12.4 pts (5.1 pts below line; 64% blended confidence). Risk: L3 has surged to 21.3 after a 6-pt performance (4.7 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10427,36 +10587,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.571</v>
+        <v>0.535</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>18.4</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
-        <v>1.877</v>
+        <v>2.9</v>
       </c>
       <c r="K66" t="n">
-        <v>1.855</v>
+        <v>1.385</v>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>Williamson shows low scoring variance (σ=4.1) — highly predictable output. His H2H avg of 21.7 pts is 1.6 above his season L30; His TS% shifts -14.6% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 18.4 pts (2.1 pts below line; 57% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>III shows low scoring variance (σ=4.4) — highly predictable output. His H2H avg of 4.7 pts is 2.7 below his season L30; His TS% shifts -7.0% in this matchup. Opponent ranks as weak defense (#25) with above-average pace (#7). 6/10 signals agree — HR L30, HR L10, Trend support under; Volume, Defense against. Projection model targets 5.2 pts (1.3 pts below line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10471,40 +10631,40 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.542</v>
+        <v>0.633</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>18.5</v>
+        <v>24.1</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="K67" t="n">
-        <v>1.87</v>
+        <v>1.385</v>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>Murray shows recent scoring down 4.6 pts vs L30 (L5 vs L30 trend). FG% trend +3.9% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 18.5 pts (2.0 pts above line; 54% blended confidence). Risk: L3 has dropped to 12.7 (5.3 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>III's L30 average of 22.8 pts is 3.3 above the 19.5 line, supports the OVER. Opponent ranks as below-average defense (#20) with moderate pace (#18). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, H2H against. Projection model targets 24.1 pts (4.6 pts above line; 63% blended confidence). Risk: L3 has dropped to 17.7 (5.1 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10514,7 +10674,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -10523,36 +10683,36 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.52</v>
+        <v>0.571</v>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>18.4</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
-        <v>1.758</v>
+        <v>2.9</v>
       </c>
       <c r="K68" t="n">
-        <v>1.98</v>
+        <v>1.385</v>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>Camara shows recent scoring up 5.5 pts vs L30 (L5 vs L30 trend). His TS% shifts +7.1% in this matchup; FG% trend +8.8% (L10 vs L30). Opponent ranks as below-average defense (#22) with above-average pace (#7). 6/10 signals agree — HR L10, Trend, Context support over; Volume, HR L30 against. Projection model targets 14.0 pts (0.5 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=8.8) introduces outcome uncertainty.</t>
+          <t>Williamson shows low scoring variance (σ=4.1) — highly predictable output. His H2H avg of 21.7 pts is 1.6 above his season L30; His TS% shifts -14.6% in this matchup. Opponent ranks as below-average defense (#20) with moderate pace (#18). Mixed signal picture: 3/10 agree. Agreeing: Volume, Context, Pace. Counter-signals: HR L30, HR L10, Trend. Projection model targets 18.4 pts (2.1 pts below line; 57% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10562,7 +10722,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10571,7 +10731,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.549</v>
+        <v>0.542</v>
       </c>
       <c r="F69" t="n">
         <v>5</v>
@@ -10580,32 +10740,32 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>5.8</v>
+        <v>18.5</v>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>2.02</v>
+        <v>3.05</v>
       </c>
       <c r="K69" t="n">
-        <v>1.735</v>
+        <v>1.357</v>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>Thybulle shows low scoring variance (σ=3.5) — highly predictable output. Opponent ranks as weak defense (#23) with above-average pace (#7). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 5.8 pts (1.7 pts below line; 54% blended confidence).</t>
+          <t>Murray shows recent scoring down 4.6 pts vs L30 (L5 vs L30 trend). FG% trend +3.9% (L10 vs L30). Opponent ranks as below-average defense (#20) with moderate pace (#18). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 18.5 pts (2.0 pts above line; 54% blended confidence). Risk: L3 has dropped to 12.7 (5.3 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10628,32 +10788,32 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>11.8</v>
+        <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="K70" t="n">
-        <v>1.758</v>
+        <v>1.408</v>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>Johnson shows recent scoring up 3.3 pts vs L30 (L5 vs L30 trend). FG% trend +5.4% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#26). 6/10 signals agree — Volume, HR L10, Trend support over; HR L30, Defense against. Projection model targets 11.8 pts (0.3 pts above line; 52% blended confidence).</t>
+          <t>Camara shows recent scoring up 5.5 pts vs L30 (L5 vs L30 trend). His TS% shifts +7.1% in this matchup; FG% trend +8.8% (L10 vs L30). Opponent ranks as below-average defense (#22) with above-average pace (#7). 6/10 signals agree — HR L10, Trend, Context support over; Volume, HR L30 against. Projection model targets 14.0 pts (0.5 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=8.8) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10667,36 +10827,36 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.516</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>9.9</v>
+        <v>5.8</v>
       </c>
       <c r="I71" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="K71" t="n">
-        <v>1.364</v>
+        <v>1.658</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>Vassell's L30 average of 12.7 pts vs line of 12.5, works against the UNDER. His TS% shifts -7.8% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 4/10 agree. Agreeing: Trend, Context, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.9 pts (2.6 pts below line; 56% blended confidence).</t>
+          <t>Thybulle shows low scoring variance (σ=3.5) — highly predictable output. Opponent ranks as weak defense (#23) with above-average pace (#7). 5/10 signals agree — Volume, HR L30, HR L10 support under; Trend, Defense against. Projection model targets 5.8 pts (0.7 pts below line; 51% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10706,7 +10866,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10715,36 +10875,36 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.609</v>
+        <v>0.52</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>8.1</v>
+        <v>11.8</v>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J72" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="K72" t="n">
-        <v>1.345</v>
+        <v>1.787</v>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>Harper's L30 average of 12.6 pts vs line of 11.5, works against the UNDER. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 1/10 agree. Agreeing: Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.1 pts (3.4 pts below line; 60% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
+          <t>Johnson shows recent scoring up 3.3 pts vs L30 (L5 vs L30 trend). FG% trend +5.4% (L10 vs L30). Opponent ranks as elite defense (#4) with slow pace (#26). 6/10 signals agree — Volume, HR L10, Trend support over; HR L30, Defense against. Projection model targets 11.8 pts (0.3 pts above line; 52% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10754,7 +10914,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10763,7 +10923,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.519</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F73" t="n">
         <v>4</v>
@@ -10772,10 +10932,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>16</v>
+        <v>9.9</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J73" t="n">
         <v>3.05</v>
@@ -10785,14 +10945,14 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>Fox has a H2H avg of 24.2 pts vs this opponent (+8.7 vs line) — supporting the OVER. His H2H avg of 24.2 pts is 8.1 above his season L30; His TS% shifts +4.0% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Defense. Counter-signals: HR L30, HR L10, Trend. Projection model targets 16.0 pts (0.5 pts above line; 51% blended confidence). Risk: L3 has dropped to 10.0 (6.1 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>Vassell's L30 average of 12.7 pts vs line of 12.5, works against the UNDER. His TS% shifts -7.8% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 4/10 agree. Agreeing: Trend, Context, Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 9.9 pts (2.6 pts below line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10802,7 +10962,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10811,36 +10971,36 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.546</v>
+        <v>0.609</v>
       </c>
       <c r="F74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>16.7</v>
+        <v>8.1</v>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="K74" t="n">
-        <v>1.4</v>
+        <v>1.345</v>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>Castle shows recent scoring up 2.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.6% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Pace, FG Trend dissent. Projection model targets 16.7 pts (1.2 pts above line; 54% blended confidence).</t>
+          <t>Harper's L30 average of 12.6 pts vs line of 11.5, works against the UNDER. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 1/10 agree. Agreeing: Pace. Counter-signals: Volume, HR L30, HR L10. Projection model targets 8.1 pts (3.4 pts below line; 60% blended confidence). Risk: 65% hit rate over L30 suggests line may already price in OVER tendency.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10859,36 +11019,36 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.519</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="K75" t="n">
-        <v>1.408</v>
+        <v>1.357</v>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>Barnes has a H2H avg of 12.4 pts vs this opponent (+4.9 vs line) — supporting the OVER. His H2H avg of 12.4 pts is 3.7 above his season L30; His TS% shifts +13.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 9.6 pts (2.1 pts above line; 56% blended confidence).</t>
+          <t>Fox has a H2H avg of 24.2 pts vs this opponent (+8.7 vs line) — supporting the OVER. His H2H avg of 24.2 pts is 8.1 above his season L30; His TS% shifts +4.0% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). Mixed signal picture: 4/10 agree. Agreeing: Volume, Context, Defense. Counter-signals: HR L30, HR L10, Trend. Projection model targets 16.0 pts (0.5 pts above line; 51% blended confidence). Risk: L3 has dropped to 10.0 (6.1 below L30) — if the slump deepens, this over is vulnerable.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10898,7 +11058,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10907,36 +11067,36 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.571</v>
+        <v>0.546</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>14.2</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K76" t="n">
-        <v>1.364</v>
+        <v>1.345</v>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>Mathurin has a H2H avg of 12.6 pts vs this opponent (-3.9 vs line) — supporting the UNDER. His H2H avg of 12.6 pts is 5.7 below his season L30; His TS% shifts -4.3% in this matchup. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.2 pts (2.3 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.2) introduces outcome uncertainty.</t>
+          <t>Castle shows recent scoring up 2.3 pts vs L30 (L5 vs L30 trend). His TS% shifts +4.6% in this matchup. Opponent ranks as below-average defense (#20) with slow pace (#26). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Pace, FG Trend dissent. Projection model targets 16.7 pts (1.2 pts above line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10955,7 +11115,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.535</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F77" t="n">
         <v>5</v>
@@ -10964,27 +11124,27 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="K77" t="n">
-        <v>1.4</v>
+        <v>1.417</v>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>Collins has a H2H avg of 15.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His TS% shifts -3.6% in this matchup; FG% trend -9.9% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 12.5 pts (1.0 pts above line; 53% blended confidence).</t>
+          <t>Barnes has a H2H avg of 12.4 pts vs this opponent (+4.9 vs line) — supporting the OVER. His H2H avg of 12.4 pts is 3.7 above his season L30; His TS% shifts +13.8% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 5/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 9.6 pts (2.1 pts above line; 56% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10994,7 +11154,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11003,36 +11163,36 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.538</v>
+        <v>0.571</v>
       </c>
       <c r="F78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>10.5</v>
+        <v>14.2</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K78" t="n">
-        <v>1.435</v>
+        <v>1.357</v>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>Champagnie shows low scoring variance (σ=4.1) — highly predictable output. Opponent ranks as elite defense (#4) with slow pace (#26). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 10.5 pts (1.0 pts above line; 53% blended confidence).</t>
+          <t>Mathurin has a H2H avg of 12.6 pts vs this opponent (-3.9 vs line) — supporting the UNDER. His H2H avg of 12.6 pts is 5.7 below his season L30; His TS% shifts -4.3% in this matchup. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Trend, Defense, H2H. Counter-signals: Volume, HR L30, HR L10. Projection model targets 14.2 pts (2.3 pts below line; 57% blended confidence). Risk: high scoring volatility (σ=7.2) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -11047,40 +11207,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.621</v>
+        <v>0.535</v>
       </c>
       <c r="F79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="I79" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="K79" t="n">
-        <v>1.345</v>
+        <v>1.417</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>Lopez shows recent scoring up 4.5 pts vs L30 (L5 vs L30 trend). His H2H avg of 14.2 pts is 3.7 above his season L30; His TS% shifts +4.3% in this matchup. Opponent ranks as below-average defense (#18) with above-average pace (#9). 7/10 signals agree (Trend, Context, Defense, H2H among the strongest); Volume, HR L30 dissent. Projection model targets 14.6 pts (4.1 pts above line; 62% blended confidence).</t>
+          <t>Collins has a H2H avg of 15.6 pts vs this opponent (+4.1 vs line) — supporting the OVER. His TS% shifts -3.6% in this matchup; FG% trend -9.9% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 12.5 pts (1.0 pts above line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -11090,7 +11250,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11099,36 +11259,36 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="I80" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="K80" t="n">
-        <v>1.345</v>
+        <v>1.556</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>Garland has a H2H avg of 17.2 pts vs this opponent (-2.3 vs line) — supporting the UNDER. His H2H avg of 17.2 pts is 3.5 below his season L30; His TS% shifts -11.0% in this matchup. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Defense, H2H, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 17.0 pts (2.5 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=8.3) introduces outcome uncertainty.</t>
+          <t>Champagnie shows low scoring variance (σ=4.1) — highly predictable output. Opponent ranks as elite defense (#4) with slow pace (#26). 8/10 signals agree (Volume, HR L30, HR L10, Trend among the strongest); Defense, Pace dissent. Projection model targets 10.5 pts (1.0 pts above line; 53% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -11143,40 +11303,40 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.516</v>
+        <v>0.621</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
-        <v>25.4</v>
+        <v>14.6</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J81" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="K81" t="n">
-        <v>1.408</v>
+        <v>1.345</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Wembanyama shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). His TS% shifts -3.1% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 5/10 signals agree — Volume, HR L30, Trend support over; HR L10, Defense against. Projection model targets 25.4 pts (0.9 pts above line; 51% blended confidence). Risk: high scoring volatility (σ=8.9) introduces outcome uncertainty.</t>
+          <t>Lopez shows recent scoring up 4.5 pts vs L30 (L5 vs L30 trend). His H2H avg of 14.2 pts is 3.7 above his season L30; His TS% shifts +4.3% in this matchup. Opponent ranks as below-average defense (#18) with above-average pace (#9). 7/10 signals agree (Trend, Context, Defense, H2H among the strongest); Volume, HR L30 dissent. Projection model targets 14.6 pts (4.1 pts above line; 62% blended confidence).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -11186,7 +11346,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11195,36 +11355,36 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.548</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K82" t="n">
-        <v>1.385</v>
+        <v>1.357</v>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Dunn has a H2H avg of 7.4 pts vs this opponent (+2.9 vs line) — supporting the OVER. FG% trend -6.7% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 6.1 pts (1.6 pts above line; 54% blended confidence).</t>
+          <t>Garland has a H2H avg of 17.2 pts vs this opponent (-2.3 vs line) — supporting the UNDER. His H2H avg of 17.2 pts is 3.5 below his season L30; His TS% shifts -11.0% in this matchup. Opponent ranks as strong defense (#8) with above-average pace (#9). Mixed signal picture: 3/10 agree. Agreeing: Defense, H2H, Min Trend. Counter-signals: Volume, HR L30, HR L10. Projection model targets 17.0 pts (2.5 pts below line; 56% blended confidence). Risk: high scoring volatility (σ=8.3) introduces outcome uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -11234,7 +11394,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11243,7 +11403,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.508</v>
+        <v>0.497</v>
       </c>
       <c r="F83" t="n">
         <v>6</v>
@@ -11252,27 +11412,27 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>27.8</v>
+        <v>25.3</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K83" t="n">
-        <v>1.364</v>
+        <v>1.385</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>[Low conviction — lean only] Leonard shows recent scoring down 2.7 pts vs L30 (L5 vs L30 trend). Opponent ranks as strong defense (#8) with above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 27.8 pts (0.3 pts above line; 50% blended confidence). Risk: L3 has dropped to 23.7 (4.2 below L30) — if the slump deepens, this over is vulnerable.</t>
+          <t>[Low conviction — lean only] Wembanyama shows recent scoring up 5.0 pts vs L30 (L5 vs L30 trend). His TS% shifts -3.1% in this matchup. Opponent ranks as elite defense (#4) with slow pace (#26). 6/10 signals agree — Volume, Context, Defense support under; HR L30, HR L10 against. Projection model targets 25.3 pts (0.2 pts below line; 49% blended confidence). Risk: L3 has surged to 35.0 after a 28-pt performance (10.0 above L30) — if that momentum carries, this under is at risk.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -11282,38 +11442,134 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_LEAN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.522</v>
+        <v>0.508</v>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>[Low conviction — lean only] Leonard shows recent scoring down 2.7 pts vs L30 (L5 vs L30 trend). Opponent ranks as strong defense (#8) with above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 27.8 pts (0.3 pts above line; 50% blended confidence). Risk: L3 has dropped to 23.7 (4.2 below L30) — if the slump deepens, this over is vulnerable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Derrick Jones Jr.</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>T3_LEAN</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="I84" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>Jr. shows recent scoring down 5.4 pts vs L30 (L5 vs L30 trend). His TS% shifts -14.5% in this matchup; FG% trend -10.0% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 5/10 signals agree — Volume, HR L30, Context support over; HR L10, Trend against. Projection model targets 9.3 pts (0.8 pts above line; 52% blended confidence). Risk: L3 has dropped to 6.0 (4.8 below L30) — if the slump deepens, this over is vulnerable.</t>
+      <c r="I85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1.408</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>[Low conviction — lean only] Jr. shows recent scoring down 5.4 pts vs L30 (L5 vs L30 trend). His TS% shifts -14.5% in this matchup; FG% trend -10.0% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 5/10 signals agree — HR L10, Trend, Defense support under; Volume, HR L30 against. Projection model targets 9.3 pts (0.2 pts below line; 51% blended confidence). Risk: 60% hit rate over L30 suggests line may already price in OVER tendency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Dunn has a H2H avg of 7.4 pts vs this opponent (+2.9 vs line) — supporting the OVER. FG% trend -6.7% (L10 vs L30). Opponent ranks as strong defense (#8) with above-average pace (#9). 6/10 signals agree — Volume, HR L30, HR L10 support over; Trend, Defense against. Projection model targets 6.1 pts (1.6 pts above line; 54% blended confidence).</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11426,7 +11682,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Grayson Allen</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11440,13 +11696,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Devin Booker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11460,13 +11716,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jalen Green</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11476,17 +11732,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devin Booker</t>
+          <t>Moussa Diabaté</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11496,17 +11752,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Coby White</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11520,13 +11776,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moussa Diabaté</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11540,13 +11796,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coby White</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11556,17 +11812,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Royce O'Neale</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11580,13 +11836,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Collin Gillespie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11596,17 +11852,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dillon Brooks</t>
+          <t>Miles Bridges</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11616,17 +11872,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Royce O'Neale</t>
+          <t>Grayson Allen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -11636,17 +11892,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Collin Gillespie</t>
+          <t>Jalen Green</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -11656,17 +11912,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Miles Bridges</t>
+          <t>Dillon Brooks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11676,11 +11932,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="17">
@@ -11800,7 +12056,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="23">
@@ -11920,7 +12176,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="29">
@@ -12000,7 +12256,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="33">
@@ -12026,7 +12282,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alex Caruso</t>
+          <t>Ajay Mitchell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -12036,17 +12292,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ajay Mitchell</t>
+          <t>Jalen Williams</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12060,13 +12316,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jalen Williams</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -12076,17 +12332,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12100,13 +12356,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Shai Gilgeous-Alexander</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12116,17 +12372,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Luka Dončić</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12136,17 +12392,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luka Dončić</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12160,13 +12416,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12180,13 +12436,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12200,7 +12456,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43">
@@ -12246,7 +12502,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Alex Caruso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12256,11 +12512,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="46">
@@ -12280,7 +12536,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="47">
@@ -12420,7 +12676,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="54">
@@ -12466,47 +12722,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Saddiq Bey</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Herbert Jones</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NOP @ POR</t>
+          <t>CLE @ GSW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>LEAN OVER</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Scoot Henderson</t>
+          <t>Saddiq Bey</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12516,7 +12772,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -12526,7 +12782,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deni Avdija</t>
+          <t>Herbert Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12540,13 +12796,13 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Yves Missi</t>
+          <t>Scoot Henderson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12560,13 +12816,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Donovan Clingan</t>
+          <t>Deni Avdija</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12580,13 +12836,13 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Derik Queen</t>
+          <t>Yves Missi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12596,17 +12852,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jrue Holiday</t>
+          <t>Donovan Clingan</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12620,13 +12876,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Robert Williams III</t>
+          <t>Derik Queen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12636,17 +12892,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trey Murphy III</t>
+          <t>Jrue Holiday</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12656,17 +12912,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Zion Williamson</t>
+          <t>Robert Williams III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -12680,13 +12936,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dejounte Murray</t>
+          <t>Trey Murphy III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -12700,13 +12956,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Toumani Camara</t>
+          <t>Zion Williamson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -12716,17 +12972,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matisse Thybulle</t>
+          <t>Dejounte Murray</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12736,22 +12992,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Keldon Johnson</t>
+          <t>Toumani Camara</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -12760,18 +13016,18 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Devin Vassell</t>
+          <t>Matisse Thybulle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAS @ LAC</t>
+          <t>NOP @ POR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -12780,13 +13036,13 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dylan Harper</t>
+          <t>Keldon Johnson</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12796,7 +13052,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -12806,7 +13062,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>De'Aaron Fox</t>
+          <t>Devin Vassell</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12816,17 +13072,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Stephon Castle</t>
+          <t>Dylan Harper</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12836,17 +13092,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Harrison Barnes</t>
+          <t>De'Aaron Fox</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -12860,13 +13116,13 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Stephon Castle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -12876,17 +13132,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>John Collins</t>
+          <t>Harrison Barnes</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -12900,13 +13156,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Julian Champagnie</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12916,17 +13172,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>John Collins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -12940,13 +13196,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Darius Garland</t>
+          <t>Julian Champagnie</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -12956,17 +13212,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Victor Wembanyama</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -12980,13 +13236,13 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>24.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Darius Garland</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -12996,17 +13252,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Victor Wembanyama</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -13016,31 +13272,71 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LEAN OVER</t>
+          <t>LEAN UNDER</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Kawhi Leonard</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LEAN OVER</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LEAN UNDER</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Kris Dunn</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAS @ LAC</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>8.5</v>
+      <c r="D86" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>

--- a/daily/2026-04-02.xlsx
+++ b/daily/2026-04-02.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
         <bgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+        <bgColor rgb="0022C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -66,6 +78,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -629,7 +643,6 @@
       <c r="V2" t="n">
         <v>21</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
         <v>0</v>
       </c>
@@ -707,7 +720,6 @@
       <c r="V3" t="n">
         <v>22</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>54</v>
       </c>
@@ -949,7 +961,6 @@
       <c r="V6" t="n">
         <v>22</v>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>-11</v>
       </c>
@@ -1027,7 +1038,6 @@
       <c r="V7" t="n">
         <v>22</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>-35.6</v>
       </c>
@@ -1187,7 +1197,6 @@
       <c r="V9" t="n">
         <v>22</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>-9.199999999999999</v>
       </c>
@@ -1347,7 +1356,6 @@
       <c r="V11" t="n">
         <v>21</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>-13.4</v>
       </c>
@@ -1425,7 +1433,6 @@
       <c r="V12" t="n">
         <v>21</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>16.1</v>
       </c>
@@ -1585,7 +1592,6 @@
       <c r="V14" t="n">
         <v>21</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>12.8</v>
       </c>
@@ -1745,7 +1751,6 @@
       <c r="V16" t="n">
         <v>21</v>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>-38</v>
       </c>
@@ -1905,7 +1910,6 @@
       <c r="V18" t="n">
         <v>16</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>-9.4</v>
       </c>
@@ -2065,7 +2069,6 @@
       <c r="V20" t="n">
         <v>16</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>0.8</v>
       </c>
@@ -2471,7 +2474,6 @@
       <c r="V25" t="n">
         <v>19</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>-27.8</v>
       </c>
@@ -2631,7 +2633,6 @@
       <c r="V27" t="n">
         <v>16</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -2709,7 +2710,6 @@
       <c r="V28" t="n">
         <v>19</v>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>7.9</v>
       </c>
@@ -3197,7 +3197,6 @@
       <c r="V34" t="n">
         <v>17</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>-7.3</v>
       </c>
@@ -4177,7 +4176,6 @@
       <c r="V46" t="n">
         <v>10</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-30.4</v>
       </c>
@@ -4337,7 +4335,6 @@
       <c r="V48" t="n">
         <v>12</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>-1</v>
       </c>
@@ -4661,7 +4658,6 @@
       <c r="V52" t="n">
         <v>10</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>0.5</v>
       </c>
@@ -4739,7 +4735,6 @@
       <c r="V53" t="n">
         <v>12</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>-34.3</v>
       </c>
@@ -4899,7 +4894,6 @@
       <c r="V55" t="n">
         <v>12</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>-3.4</v>
       </c>
@@ -4977,7 +4971,6 @@
       <c r="V56" t="n">
         <v>10</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>-2.9</v>
       </c>
@@ -5137,7 +5130,6 @@
       <c r="V58" t="n">
         <v>18</v>
       </c>
-      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>0.7</v>
       </c>
@@ -5625,7 +5617,6 @@
       <c r="V64" t="n">
         <v>18</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>14.2</v>
       </c>
@@ -5867,7 +5858,6 @@
       <c r="V67" t="n">
         <v>18</v>
       </c>
-      <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
         <v>5</v>
       </c>
@@ -6027,7 +6017,6 @@
       <c r="V69" t="n">
         <v>18</v>
       </c>
-      <c r="W69" t="inlineStr"/>
       <c r="X69" t="n">
         <v>15.6</v>
       </c>
@@ -6187,7 +6176,6 @@
       <c r="V71" t="n">
         <v>7</v>
       </c>
-      <c r="W71" t="inlineStr"/>
       <c r="X71" t="n">
         <v>0</v>
       </c>
@@ -6429,7 +6417,6 @@
       <c r="V74" t="n">
         <v>26</v>
       </c>
-      <c r="W74" t="inlineStr"/>
       <c r="X74" t="n">
         <v>8</v>
       </c>
@@ -6982,7 +6969,7 @@
         <v>50</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>4.5</v>
@@ -7245,7 +7232,6 @@
       <c r="V84" t="n">
         <v>9</v>
       </c>
-      <c r="W84" t="inlineStr"/>
       <c r="X84" t="n">
         <v>2.4</v>
       </c>
@@ -11640,523 +11626,1199 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Mark Williams</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 7.5 line, +4.5). Projection model (6.9 pts) and actual (12) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Grant Williams</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (10 pts vs 5.5 line, +4.5). Projection model (4.6 pts) and actual (10) both missed the mark. Key signals that disagreed: Volume, HR L30, HR L10. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 20.5 line, -5.5). Projection model targeted 23.1 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Devin Booker</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (22 pts vs 25.5 line, -3.5). Projection model targeted 33.5 pts (correct direction) but actual was 22. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Ryan Kalkbrenner</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (8 pts vs 5.5 line, +2.5). Projection model called 6.1 pts — actual 8 was 1.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 7.5 line, -3.5). Projection model called 2.7 pts — actual 4 was 1.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (19 pts vs 13.5 line, +5.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (20 pts vs 16.5 line, +3.5). Projection model targeted 10.7 pts (correct direction) but actual was 20. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (17 pts vs 19.5 line, -2.5).</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Royce O'Neale</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (3 pts vs 7.5 line, -4.5). Projection model called 3.6 pts — actual 3 was 0.6 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Collin Gillespie</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 10.5 line, -4.5). Projection model targeted 18.3 pts (correct direction) but actual was 6. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 13.5 line, +11.5).</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Grayson Allen</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 12.5 line, +0.5). Projection model called 16.0 pts — actual 13 was 3.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Jalen Green</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 16.5 line, +8.5). Overperformed by 8.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Dillon Brooks</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PHX @ CHA</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 14.5 line, -1.5).</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Jalen Duren</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (22 pts vs 22.5 line, -0.5).</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Paul Reed</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (4 pts vs 7.5 line, -3.5). Projection model (7.7 pts) and actual (4) both missed the mark. Key signals that disagreed: Defense, H2H, Pace. Counter-signals that proved correct: Defense, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ausar Thompson</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 9.5 line, -2.5). Projection model called 8.2 pts — actual 7 was 1.2 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Daniss Jenkins</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (26 pts vs 16.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Rudy Gobert</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 10.5 line, -4.5). Projection model targeted 12.1 pts (correct direction) but actual was 6. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Defense, Pace, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Donte DiVincenzo</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 11.5 line, -6.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Duncan Robinson</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (15 pts vs 11.5 line, +3.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Julius Randle</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (27 pts vs 19.5 line, +7.5). Projection model targeted 16.4 pts (correct direction) but actual was 27. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Bones Hyland</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E25" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 10.5 line, -4.5). Projection model called 6.2 pts — actual 6 was 0.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Kevin Huerter</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (12 pts vs 7.5 line, +4.5). Projection model targeted 4.1 pts (correct direction) but actual was 12. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Tobias Harris</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>14.5</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (2 pts vs 14.5 line, -12.5). Underperformed by 12.5 pts — potentially a blowout or garbage-time scenario that pulled starters early. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -12178,325 +12840,753 @@
       <c r="D28" t="n">
         <v>25.5</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Ayo Dosunmu</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (19 pts vs 15.5 line, +3.5).</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Naz Reid</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>MIN @ DET</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E30" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 12.5 line, +6.5). Projection model targeted 4.4 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: FG Trend, Min Trend.</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (7 pts vs 6.5 line, +0.5). Projection model called 6.9 pts — actual 7 was 0.1 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (7 pts vs 15.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (14 pts vs 6.5 line, +7.5).</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 12.5 line, -2.5). Projection model called 9.7 pts — actual 10 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (10 pts vs 18.5 line, -8.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (8 pts vs 6.5 line, +1.5). Projection model called 8.3 pts — actual 8 was 0.3 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>30.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (28 pts vs 30.5 line, -2.5). Projection model (31.2 pts) and actual (28) both missed the mark. Key signals that disagreed: HR L30, HR L10, Defense. Counter-signals that proved correct: HR L30, HR L10, Defense.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (4 pts vs 8.5 line, -4.5). Projection model (8.5 pts) and actual (4) both missed the mark. Key signals that disagreed: HR L30, HR L10, Trend. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Luka Dončić</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>31.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 31.5 line, -19.5).</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E40" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (13 pts vs 17.5 line, -4.5). Projection model called 15.2 pts — actual 13 was 2.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Austin Reaves</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (15 pts vs 19.5 line, -4.5). Projection model called 15.5 pts — actual 15 was 0.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 9.5 line, -1.5). Projection model called 6.0 pts — actual 8 was 2.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 6.5 line, -0.5). Projection model called 4.8 pts — actual 6 was 1.2 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Jaxson Hayes</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>LAL @ OKC</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="4" t="n">
         <v>5.5</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 5.5 line, +6.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -12518,745 +13608,1719 @@
       <c r="D45" t="n">
         <v>4.5</v>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (8 pts vs 9.5 line, -1.5).</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Donovan Mitchell</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E47" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 24.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Jarrett Allen</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (16 pts vs 13.5 line, +2.5). Projection model called 13.6 pts — actual 16 was 2.4 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Dennis Schröder</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 6.5 line, +5.5). Projection model called 12.1 pts — actual 12 was 0.1 off. Model accuracy strong on this play. Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Evan Mobley</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (12 pts vs 17.5 line, -5.5). Projection model called 15.0 pts — actual 12 was 3.0 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (16 pts vs 19.5 line, -3.5). Projection model called 15.3 pts — actual 16 was 0.7 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (25 pts vs 15.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Max Strus</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (24 pts vs 9.5 line, +14.5). Overperformed by 14.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>James Harden</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (19 pts vs 19.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: HR L30, HR L10, Trend.</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Sam Merrill</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (3 pts vs 11.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E56" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (5 pts vs 13.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>CLE @ GSW</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (25 pts vs 14.5 line, +10.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (15 pts vs 17.5 line, -2.5). Projection model targeted 21.9 pts (correct direction) but actual was 15. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (9 pts vs 9.5 line, -0.5). Projection model called 6.5 pts — actual 9 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (14 pts vs 16.5 line, -2.5). Projection model called 12.1 pts — actual 14 was 1.9 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (26 pts vs 26.5 line, -0.5). Signal alignment was sound — 7/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Yves Missi</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (6 pts vs 5.5 line, +0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Volume, HR L10, Defense.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E63" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 13.5 line, -9.5).</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (12 pts vs 8.5 line, +3.5).</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (27 pts vs 17.5 line, +9.5). Overperformed by 9.5 pts — unexpected scoring burst, possibly vs a blowout or pace mismatch. Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>BLOWOUT_EFFECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (6 pts vs 6.5 line, -0.5). Projection model called 5.2 pts — actual 6 was 0.8 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (19 pts vs 19.5 line, -0.5). Missed by 0.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, H2H, Pace.</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (15 pts vs 20.5 line, -5.5).</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Dejounte Murray</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (9 pts vs 16.5 line, -7.5). Projection model targeted 18.5 pts (correct direction) but actual was 9. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: HR L10, Trend, H2H.</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E70" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (23 pts vs 13.5 line, +9.5).</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Matisse Thybulle</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>NOP @ POR</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (13 pts vs 6.5 line, +6.5). Projection model (5.8 pts) and actual (13) both missed the mark. Key signals that disagreed: Trend, Defense, H2H. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Keldon Johnson</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E72" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 11.5 line, +1.5). Projection model called 11.8 pts — actual 13 was 1.2 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Devin Vassell</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E73" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (14 pts vs 12.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Dylan Harper</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (19 pts vs 11.5 line, +7.5). Projection model targeted 8.1 pts (correct direction) but actual was 19. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>De'Aaron Fox</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (22 pts vs 15.5 line, +6.5).</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Stephon Castle</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E76" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (20 pts vs 15.5 line, +4.5). Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Harrison Barnes</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 7.5 line, -4.5). Projection model targeted 9.6 pts (correct direction) but actual was 3. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Trend, Defense, Pace.</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: UNDER missed (18 pts vs 16.5 line, +1.5). Missed by 1.5 pts — a close call. Direction was questionable (signals were mixed). Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (15 pts vs 11.5 line, +3.5). Projection model called 12.5 pts — actual 15 was 2.5 off. Model accuracy strong on this play.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Julian Champagnie</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E80" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>WIN: OVER hit (13 pts vs 9.5 line, +3.5). Projection model called 10.5 pts — actual 13 was 2.5 off. Model accuracy strong on this play. Signal alignment was sound — 8/10 signals were correct.</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (6 pts vs 10.5 line, -4.5). Projection model targeted 14.6 pts (correct direction) but actual was 6. Likely shooting variance — per-minute output may have been on pace. Counter-signals that proved correct: Volume, HR L30, HR L10.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="4" t="n">
         <v>19.5</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (11 pts vs 19.5 line, -8.5).</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -13278,65 +15342,155 @@
       <c r="D83" t="n">
         <v>25.5</v>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>27.5</v>
       </c>
+      <c r="E84" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (24 pts vs 27.5 line, -3.5). Projection model (27.8 pts) and actual (24) both missed the mark. Key signals that disagreed: Trend, Defense, H2H. Counter-signals that proved correct: Trend, Defense, H2H.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E85" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>WIN: UNDER hit (4 pts vs 9.5 line, -5.5).</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>SAS @ LAC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="3" t="n">
         <v>4.5</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>LOSS: OVER missed (3 pts vs 4.5 line, -1.5). Missed by 1.5 pts — a close call. Direction was sound, narrowly missed execution. Counter-signals that proved correct: Trend, Defense, FG Trend.</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 07:30</t>
+        </is>
       </c>
     </row>
   </sheetData>
